--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Instrutor\Desktop\senai2025\ds\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9F82C6-6197-4AED-9E16-69865BAA0FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACE0E21-5316-44AC-B638-56E75D673C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="45">
   <si>
     <t>Alunos</t>
   </si>
@@ -221,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -236,6 +236,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -594,32 +597,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AR34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" style="1"/>
-    <col min="7" max="11" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="7.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="7.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="31" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="35" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.6640625" style="1"/>
-    <col min="38" max="39" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.6640625" style="1"/>
-    <col min="41" max="42" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="6.6640625" style="1"/>
+    <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" style="1"/>
+    <col min="7" max="11" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="31" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="35" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.7109375" style="1"/>
+    <col min="38" max="39" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.7109375" style="1"/>
+    <col min="41" max="42" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="6.7109375" style="1"/>
+    <col min="44" max="44" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="45" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -745,9 +750,11 @@
       <c r="AQ1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AR1" s="2"/>
-    </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AR1" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
@@ -877,8 +884,11 @@
       <c r="AQ2" s="2">
         <v>45833</v>
       </c>
-    </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AR2" s="6">
+        <v>45867</v>
+      </c>
+    </row>
+    <row r="3" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>24126008</v>
       </c>
@@ -1008,8 +1018,11 @@
       <c r="AQ3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AR3" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>24125990</v>
       </c>
@@ -1139,8 +1152,11 @@
       <c r="AQ4" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AR4" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>24125969</v>
       </c>
@@ -1270,8 +1286,11 @@
       <c r="AQ5" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AR5" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>24125996</v>
       </c>
@@ -1401,8 +1420,11 @@
       <c r="AQ6" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AR6" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>24125975</v>
       </c>
@@ -1532,8 +1554,11 @@
       <c r="AQ7" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AR7" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>24125978</v>
       </c>
@@ -1663,8 +1688,11 @@
       <c r="AQ8" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AR8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>24125993</v>
       </c>
@@ -1794,8 +1822,11 @@
       <c r="AQ9" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AR9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>24126043</v>
       </c>
@@ -1925,8 +1956,11 @@
       <c r="AQ10" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AR10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>24125985</v>
       </c>
@@ -2056,8 +2090,11 @@
       <c r="AQ11" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AR11" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>24125984</v>
       </c>
@@ -2187,8 +2224,11 @@
       <c r="AQ12" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AR12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>24125988</v>
       </c>
@@ -2318,8 +2358,11 @@
       <c r="AQ13" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AR13" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>24126459</v>
       </c>
@@ -2449,8 +2492,11 @@
       <c r="AQ14" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AR14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>24126094</v>
       </c>
@@ -2580,8 +2626,11 @@
       <c r="AQ15" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AR15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>24126041</v>
       </c>
@@ -2711,8 +2760,11 @@
       <c r="AQ16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR16" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -2842,8 +2894,11 @@
       <c r="AQ17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -2973,8 +3028,11 @@
       <c r="AQ18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -3104,8 +3162,11 @@
       <c r="AQ19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR19" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -3235,8 +3296,11 @@
       <c r="AQ20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -3366,8 +3430,11 @@
       <c r="AQ21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -3497,8 +3564,11 @@
       <c r="AQ22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -3628,8 +3698,11 @@
       <c r="AQ23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -3759,8 +3832,11 @@
       <c r="AQ24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -3890,8 +3966,11 @@
       <c r="AQ25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR25" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -4021,8 +4100,11 @@
       <c r="AQ26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -4152,8 +4234,11 @@
       <c r="AQ27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -4283,8 +4368,11 @@
       <c r="AQ28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR28" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -4414,8 +4502,11 @@
       <c r="AQ29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -4545,8 +4636,11 @@
       <c r="AQ30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR30" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -4676,8 +4770,11 @@
       <c r="AQ31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR31" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -4807,8 +4904,11 @@
       <c r="AQ32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -4938,8 +5038,11 @@
       <c r="AQ33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -5067,6 +5170,9 @@
         <v>3</v>
       </c>
       <c r="AQ34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR34" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -5099,14 +5205,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{591F34BA-747C-4936-A2AB-1894206F09ED}">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
         <v>24126008</v>
       </c>
@@ -5118,7 +5224,7 @@
         <v>24126008,Arthur Souza de Oliveira</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>24125990</v>
       </c>
@@ -5130,7 +5236,7 @@
         <v>24125990,Beatriz Vitoria Mendes de Almeida</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>24125969</v>
       </c>
@@ -5142,7 +5248,7 @@
         <v>24125969,Catarina Silva Pereira</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>24125996</v>
       </c>
@@ -5154,7 +5260,7 @@
         <v>24125996,Crislaine Leopoldo Candido</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>24125975</v>
       </c>
@@ -5166,7 +5272,7 @@
         <v>24125975,Diego Maradona Preti Costa Figueiredo</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>24125978</v>
       </c>
@@ -5178,7 +5284,7 @@
         <v>24125978,Erick Aguiar de Souza Pinto</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>24125993</v>
       </c>
@@ -5190,7 +5296,7 @@
         <v>24125993,Evelyn Fernandes</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>24126043</v>
       </c>
@@ -5202,7 +5308,7 @@
         <v>24126043,Fernando Joaquim Mota</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>24125985</v>
       </c>
@@ -5214,7 +5320,7 @@
         <v>24125985,Hélio Alves de Oliveira</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>24125984</v>
       </c>
@@ -5226,7 +5332,7 @@
         <v>24125984,Jessé Oliveira da Silva</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>24125988</v>
       </c>
@@ -5238,7 +5344,7 @@
         <v>24125988,João Pedro Nepomuceno dos Santos</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>24126459</v>
       </c>
@@ -5250,7 +5356,7 @@
         <v>24126459,Joao Victor da Silva Angra</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>24126094</v>
       </c>
@@ -5262,7 +5368,7 @@
         <v>24126094,Justo Willian Cardoso Carneiro</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>24126041</v>
       </c>
@@ -5274,7 +5380,7 @@
         <v>24126041,Kamili Vitoria dos Santos</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>24126007</v>
       </c>
@@ -5286,7 +5392,7 @@
         <v>24126007,Kathleen Carolini Silva Miranda</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>24127560</v>
       </c>
@@ -5298,7 +5404,7 @@
         <v>24127560,Lais Nascimento Andrade</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126396</v>
       </c>
@@ -5310,7 +5416,7 @@
         <v>24126396,Larissa dos Santos da Rocha</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24125987</v>
       </c>
@@ -5322,7 +5428,7 @@
         <v>24125987,Larissa Vitoria Alves dos Santos</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24125974</v>
       </c>
@@ -5334,7 +5440,7 @@
         <v>24125974,Lizzie de Sousa</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125992</v>
       </c>
@@ -5346,7 +5452,7 @@
         <v>24125992,Maria Luiza Alves Florêncio</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125977</v>
       </c>
@@ -5358,7 +5464,7 @@
         <v>24125977,Mellyssa Eduarda de Medeiros Silveira</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125991</v>
       </c>
@@ -5370,7 +5476,7 @@
         <v>24125991,Pedro Duarde Naddeu Russo</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125989</v>
       </c>
@@ -5382,7 +5488,7 @@
         <v>24125989,Pedro Henrique de Oliveira</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125983</v>
       </c>
@@ -5394,7 +5500,7 @@
         <v>24125983,Rebeca Aparecida Lima do Nascimento</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125976</v>
       </c>
@@ -5406,7 +5512,7 @@
         <v>24125976,Rebeca Cinthia Lazarini</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125967</v>
       </c>
@@ -5418,7 +5524,7 @@
         <v>24125967,Rhayssa Rhackelly Maria</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125981</v>
       </c>
@@ -5430,7 +5536,7 @@
         <v>24125981,Rodrigo Passberg de Oliveiro</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24126030</v>
       </c>
@@ -5442,7 +5548,7 @@
         <v>24126030,Steffany Giovanna da Silva Souza</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24126277</v>
       </c>
@@ -5454,7 +5560,7 @@
         <v>24126277,Thamye Souza Correa</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24125982</v>
       </c>
@@ -5466,7 +5572,7 @@
         <v>24125982,Thiago Muniz dos Santos</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24125986</v>
       </c>
@@ -5478,7 +5584,7 @@
         <v>24125986,Vitor Alexandre Menegão Gomes</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125994</v>
       </c>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACE0E21-5316-44AC-B638-56E75D673C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E69CE0-8935-49F1-9CD6-99272FC52C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="45">
   <si>
     <t>Alunos</t>
   </si>
@@ -235,10 +235,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -596,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AR34"/>
+  <dimension ref="A1:AS34"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -624,12 +624,12 @@
     <col min="45" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
       <c r="D1" s="2" t="s">
         <v>35</v>
       </c>
@@ -750,11 +750,14 @@
       <c r="AQ1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AR1" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS1" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
@@ -884,11 +887,14 @@
       <c r="AQ2" s="2">
         <v>45833</v>
       </c>
-      <c r="AR2" s="6">
+      <c r="AR2" s="5">
         <v>45867</v>
       </c>
-    </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS2" s="5">
+        <v>45868</v>
+      </c>
+    </row>
+    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>24126008</v>
       </c>
@@ -1021,8 +1027,11 @@
       <c r="AR3" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>24125990</v>
       </c>
@@ -1155,8 +1164,11 @@
       <c r="AR4" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>24125969</v>
       </c>
@@ -1289,8 +1301,11 @@
       <c r="AR5" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>24125996</v>
       </c>
@@ -1423,8 +1438,11 @@
       <c r="AR6" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS6" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>24125975</v>
       </c>
@@ -1557,8 +1575,11 @@
       <c r="AR7" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS7" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>24125978</v>
       </c>
@@ -1691,8 +1712,11 @@
       <c r="AR8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS8" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>24125993</v>
       </c>
@@ -1825,8 +1849,11 @@
       <c r="AR9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS9" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>24126043</v>
       </c>
@@ -1959,8 +1986,11 @@
       <c r="AR10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS10" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>24125985</v>
       </c>
@@ -2093,8 +2123,11 @@
       <c r="AR11" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS11" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>24125984</v>
       </c>
@@ -2227,8 +2260,11 @@
       <c r="AR12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS12" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>24125988</v>
       </c>
@@ -2361,8 +2397,11 @@
       <c r="AR13" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS13" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>24126459</v>
       </c>
@@ -2495,8 +2534,11 @@
       <c r="AR14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS14" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>24126094</v>
       </c>
@@ -2629,8 +2671,11 @@
       <c r="AR15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS15" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>24126041</v>
       </c>
@@ -2763,8 +2808,11 @@
       <c r="AR16" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -2897,8 +2945,11 @@
       <c r="AR17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3031,8 +3082,11 @@
       <c r="AR18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -3165,8 +3219,11 @@
       <c r="AR19" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -3299,8 +3356,11 @@
       <c r="AR20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -3433,8 +3493,11 @@
       <c r="AR21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -3567,8 +3630,11 @@
       <c r="AR22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -3701,8 +3767,11 @@
       <c r="AR23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -3835,8 +3904,11 @@
       <c r="AR24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -3969,8 +4041,11 @@
       <c r="AR25" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -4103,8 +4178,11 @@
       <c r="AR26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -4237,8 +4315,11 @@
       <c r="AR27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -4371,8 +4452,11 @@
       <c r="AR28" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -4505,8 +4589,11 @@
       <c r="AR29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -4639,8 +4726,11 @@
       <c r="AR30" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -4773,8 +4863,11 @@
       <c r="AR31" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -4907,8 +5000,11 @@
       <c r="AR32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -5041,8 +5137,11 @@
       <c r="AR33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -5173,6 +5272,9 @@
         <v>3</v>
       </c>
       <c r="AR34" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AS34" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -5184,7 +5286,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:XFD1 A2:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 A3:XFD1048576 A2:AR2 AS1:XFD2">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E69CE0-8935-49F1-9CD6-99272FC52C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DA89B2-14B5-43D3-AE45-127760286CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="45">
   <si>
     <t>Alunos</t>
   </si>
@@ -221,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -239,6 +239,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -596,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AS34"/>
+  <dimension ref="A1:AU34"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -606,25 +609,16 @@
     <col min="6" max="6" width="6.7109375" style="1"/>
     <col min="7" max="11" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="17" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="31" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="35" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.7109375" style="1"/>
-    <col min="38" max="39" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.7109375" style="1"/>
-    <col min="41" max="42" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="6.7109375" style="1"/>
-    <col min="44" max="44" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="45" max="16384" width="6.7109375" style="1"/>
+    <col min="18" max="27" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="35" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="43" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="6.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="47" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -756,8 +750,14 @@
       <c r="AS1" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
@@ -893,8 +893,14 @@
       <c r="AS2" s="5">
         <v>45868</v>
       </c>
-    </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT2" s="7">
+        <v>45874</v>
+      </c>
+      <c r="AU2" s="7">
+        <v>45875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>24126008</v>
       </c>
@@ -1030,8 +1036,11 @@
       <c r="AS3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>24125990</v>
       </c>
@@ -1167,8 +1176,11 @@
       <c r="AS4" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>24125969</v>
       </c>
@@ -1304,8 +1316,11 @@
       <c r="AS5" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>24125996</v>
       </c>
@@ -1441,8 +1456,11 @@
       <c r="AS6" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT6" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>24125975</v>
       </c>
@@ -1578,8 +1596,11 @@
       <c r="AS7" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT7" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>24125978</v>
       </c>
@@ -1715,8 +1736,11 @@
       <c r="AS8" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT8" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>24125993</v>
       </c>
@@ -1852,8 +1876,11 @@
       <c r="AS9" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT9" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>24126043</v>
       </c>
@@ -1989,8 +2016,11 @@
       <c r="AS10" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT10" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>24125985</v>
       </c>
@@ -2126,8 +2156,11 @@
       <c r="AS11" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT11" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>24125984</v>
       </c>
@@ -2263,8 +2296,11 @@
       <c r="AS12" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT12" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>24125988</v>
       </c>
@@ -2400,8 +2436,11 @@
       <c r="AS13" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT13" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>24126459</v>
       </c>
@@ -2537,8 +2576,11 @@
       <c r="AS14" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT14" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>24126094</v>
       </c>
@@ -2674,8 +2716,11 @@
       <c r="AS15" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT15" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>24126041</v>
       </c>
@@ -2811,8 +2856,11 @@
       <c r="AS16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -2948,8 +2996,11 @@
       <c r="AS17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3085,8 +3136,11 @@
       <c r="AS18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -3222,8 +3276,11 @@
       <c r="AS19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -3359,8 +3416,11 @@
       <c r="AS20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -3496,8 +3556,11 @@
       <c r="AS21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -3633,8 +3696,11 @@
       <c r="AS22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -3770,8 +3836,11 @@
       <c r="AS23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -3907,8 +3976,11 @@
       <c r="AS24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -4044,8 +4116,11 @@
       <c r="AS25" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -4181,8 +4256,11 @@
       <c r="AS26" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -4318,8 +4396,11 @@
       <c r="AS27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -4455,8 +4536,11 @@
       <c r="AS28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT28" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -4592,8 +4676,11 @@
       <c r="AS29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -4729,8 +4816,11 @@
       <c r="AS30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -4866,8 +4956,11 @@
       <c r="AS31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -5003,8 +5096,11 @@
       <c r="AS32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -5140,8 +5236,11 @@
       <c r="AS33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -5275,6 +5374,9 @@
         <v>3</v>
       </c>
       <c r="AS34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT34" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -5286,7 +5388,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 A3:XFD1048576 A2:AR2 AS1:XFD2">
+  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DA89B2-14B5-43D3-AE45-127760286CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60782A4C-5E0E-4C75-A46E-4AF380FA74C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
     <sheet name="Alunos" sheetId="2" r:id="rId2"/>
+    <sheet name="Vistos4des" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="48">
   <si>
     <t>Alunos</t>
   </si>
@@ -173,6 +174,15 @@
   <si>
     <t>Fernando Joaquim Mota</t>
   </si>
+  <si>
+    <t>PP</t>
+  </si>
+  <si>
+    <t>Aluno</t>
+  </si>
+  <si>
+    <t>Aula01-Proj</t>
+  </si>
 </sst>
 </file>
 
@@ -201,12 +211,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -221,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -241,14 +257,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -599,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AU34"/>
+  <dimension ref="A1:AU39"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -893,10 +925,10 @@
       <c r="AS2" s="5">
         <v>45868</v>
       </c>
-      <c r="AT2" s="7">
+      <c r="AT2" s="2">
         <v>45874</v>
       </c>
-      <c r="AU2" s="7">
+      <c r="AU2" s="2">
         <v>45875</v>
       </c>
     </row>
@@ -1039,6 +1071,9 @@
       <c r="AT3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AU3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1179,6 +1214,9 @@
       <c r="AT4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AU4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1319,6 +1357,9 @@
       <c r="AT5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AU5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1459,6 +1500,9 @@
       <c r="AT6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AU6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1599,6 +1643,9 @@
       <c r="AT7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AU7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1739,6 +1786,9 @@
       <c r="AT8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AU8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1879,6 +1929,9 @@
       <c r="AT9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AU9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2019,6 +2072,9 @@
       <c r="AT10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AU10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2159,6 +2215,9 @@
       <c r="AT11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AU11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2299,6 +2358,9 @@
       <c r="AT12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AU12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2439,6 +2501,9 @@
       <c r="AT13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AU13" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="14" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -2579,6 +2644,9 @@
       <c r="AT14" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AU14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -2719,6 +2787,9 @@
       <c r="AT15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AU15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -2859,8 +2930,11 @@
       <c r="AT16" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -2999,8 +3073,11 @@
       <c r="AT17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3139,8 +3216,11 @@
       <c r="AT18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -3279,8 +3359,11 @@
       <c r="AT19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -3419,8 +3502,11 @@
       <c r="AT20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -3559,8 +3645,11 @@
       <c r="AT21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -3699,8 +3788,11 @@
       <c r="AT22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -3839,8 +3931,11 @@
       <c r="AT23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -3979,8 +4074,11 @@
       <c r="AT24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -4119,8 +4217,11 @@
       <c r="AT25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -4259,8 +4360,11 @@
       <c r="AT26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -4399,8 +4503,11 @@
       <c r="AT27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -4539,8 +4646,11 @@
       <c r="AT28" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="29" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -4679,8 +4789,11 @@
       <c r="AT29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -4819,8 +4932,11 @@
       <c r="AT30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -4959,8 +5075,11 @@
       <c r="AT31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -5099,8 +5218,11 @@
       <c r="AT32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -5239,8 +5361,11 @@
       <c r="AT33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="AU33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -5379,6 +5504,24 @@
       <c r="AT34" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AU34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AR35" s="8"/>
+    </row>
+    <row r="36" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AR36" s="8"/>
+    </row>
+    <row r="37" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AR37" s="8"/>
+    </row>
+    <row r="38" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AR38" s="8"/>
+    </row>
+    <row r="39" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AR39" s="8"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AQ34">
@@ -5388,16 +5531,16 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P31:P34">
-    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5802,6 +5945,201 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B32">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82759A4A-CE41-47AD-9142-A6D90AD2CAA2}">
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="7">
+        <v>45875</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A3:A34">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60782A4C-5E0E-4C75-A46E-4AF380FA74C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11E6B66-5F22-4E11-B0CB-AEB63074A9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="48">
   <si>
     <t>Alunos</t>
   </si>
@@ -254,11 +254,11 @@
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -631,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AU39"/>
+  <dimension ref="A1:BE39"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -646,16 +646,16 @@
     <col min="36" max="43" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="6.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="6.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="16384" width="6.7109375" style="1"/>
+    <col min="46" max="57" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
       <c r="D1" s="2" t="s">
         <v>35</v>
       </c>
@@ -788,8 +788,14 @@
       <c r="AU1" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
@@ -931,8 +937,22 @@
       <c r="AU2" s="2">
         <v>45875</v>
       </c>
-    </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV2" s="2">
+        <v>45876</v>
+      </c>
+      <c r="AW2" s="2">
+        <v>45877</v>
+      </c>
+      <c r="AX2" s="2"/>
+      <c r="AY2" s="2"/>
+      <c r="AZ2" s="2"/>
+      <c r="BA2" s="2"/>
+      <c r="BB2" s="2"/>
+      <c r="BC2" s="2"/>
+      <c r="BD2" s="2"/>
+      <c r="BE2" s="2"/>
+    </row>
+    <row r="3" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>24126008</v>
       </c>
@@ -1074,8 +1094,11 @@
       <c r="AU3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>24125990</v>
       </c>
@@ -1217,8 +1240,11 @@
       <c r="AU4" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>24125969</v>
       </c>
@@ -1360,8 +1386,11 @@
       <c r="AU5" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>24125996</v>
       </c>
@@ -1503,8 +1532,11 @@
       <c r="AU6" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV6" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>24125975</v>
       </c>
@@ -1646,8 +1678,11 @@
       <c r="AU7" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV7" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>24125978</v>
       </c>
@@ -1789,8 +1824,11 @@
       <c r="AU8" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV8" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>24125993</v>
       </c>
@@ -1932,8 +1970,11 @@
       <c r="AU9" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV9" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>24126043</v>
       </c>
@@ -2075,8 +2116,11 @@
       <c r="AU10" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV10" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>24125985</v>
       </c>
@@ -2218,8 +2262,11 @@
       <c r="AU11" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV11" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>24125984</v>
       </c>
@@ -2361,8 +2408,11 @@
       <c r="AU12" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV12" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>24125988</v>
       </c>
@@ -2504,8 +2554,11 @@
       <c r="AU13" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV13" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>24126459</v>
       </c>
@@ -2647,8 +2700,11 @@
       <c r="AU14" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV14" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>24126094</v>
       </c>
@@ -2790,8 +2846,11 @@
       <c r="AU15" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV15" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>24126041</v>
       </c>
@@ -2933,8 +2992,11 @@
       <c r="AU16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3076,8 +3138,11 @@
       <c r="AU17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3219,8 +3284,11 @@
       <c r="AU18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -3362,8 +3430,11 @@
       <c r="AU19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -3505,8 +3576,11 @@
       <c r="AU20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -3648,8 +3722,11 @@
       <c r="AU21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -3791,8 +3868,11 @@
       <c r="AU22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -3934,8 +4014,11 @@
       <c r="AU23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -4077,8 +4160,11 @@
       <c r="AU24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -4220,8 +4306,11 @@
       <c r="AU25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -4363,8 +4452,11 @@
       <c r="AU26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -4506,8 +4598,11 @@
       <c r="AU27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -4649,8 +4744,11 @@
       <c r="AU28" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -4792,8 +4890,11 @@
       <c r="AU29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -4935,8 +5036,11 @@
       <c r="AU30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -5078,8 +5182,11 @@
       <c r="AU31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -5221,8 +5328,11 @@
       <c r="AU32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -5364,8 +5474,11 @@
       <c r="AU33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -5507,21 +5620,24 @@
       <c r="AU34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="AR35" s="8"/>
-    </row>
-    <row r="36" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="AR36" s="8"/>
-    </row>
-    <row r="37" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="AR37" s="8"/>
-    </row>
-    <row r="38" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="AR38" s="8"/>
-    </row>
-    <row r="39" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="AR39" s="8"/>
+      <c r="AV34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AR35" s="7"/>
+    </row>
+    <row r="36" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AR36" s="7"/>
+    </row>
+    <row r="37" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AR37" s="7"/>
+    </row>
+    <row r="38" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AR38" s="7"/>
+    </row>
+    <row r="39" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AR39" s="7"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AQ34">
@@ -5531,7 +5647,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -5966,7 +6082,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" s="7">
+      <c r="B1" s="6">
         <v>45875</v>
       </c>
     </row>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11E6B66-5F22-4E11-B0CB-AEB63074A9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0E3E5C-F269-44E0-9BF6-221BEF4C3BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="49">
   <si>
     <t>Alunos</t>
   </si>
@@ -181,7 +181,10 @@
     <t>Aluno</t>
   </si>
   <si>
-    <t>Aula01-Proj</t>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Aula01-Proj Estacionamento</t>
   </si>
 </sst>
 </file>
@@ -237,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -254,11 +257,19 @@
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -651,11 +662,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
       <c r="D1" s="2" t="s">
         <v>35</v>
       </c>
@@ -5625,19 +5636,19 @@
       </c>
     </row>
     <row r="35" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AR35" s="7"/>
+      <c r="AR35" s="6"/>
     </row>
     <row r="36" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AR36" s="7"/>
+      <c r="AR36" s="6"/>
     </row>
     <row r="37" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AR37" s="7"/>
+      <c r="AR37" s="6"/>
     </row>
     <row r="38" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AR38" s="7"/>
+      <c r="AR38" s="6"/>
     </row>
     <row r="39" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AR39" s="7"/>
+      <c r="AR39" s="6"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AQ34">
@@ -5647,7 +5658,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
+  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -6078,181 +6089,215 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" s="6">
+      <c r="B1" s="9">
         <v>45875</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B2" t="s">
-        <v>47</v>
+      <c r="B2" s="8" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="B3" s="1"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="B5" s="1"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="B6" s="1"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="B7" s="1"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="B8" s="1"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="B9" s="1"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="B10" s="1"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="B11" s="1"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="B12" s="1"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="B13" s="1"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="B14" s="10"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="B15" s="1"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24" s="1"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B26" s="1"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B28" s="1"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B30" s="1"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B31" s="1"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B32" s="1"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B33" s="1"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="B34" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3:A34">

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0E3E5C-F269-44E0-9BF6-221BEF4C3BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19E8457-5C7E-4877-A907-5578DF95B7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="49">
   <si>
     <t>Alunos</t>
   </si>
@@ -240,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -261,15 +261,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -662,11 +659,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
       <c r="D1" s="2" t="s">
         <v>35</v>
       </c>
@@ -6093,7 +6090,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" s="9">
+      <c r="B1" s="8">
         <v>45875</v>
       </c>
     </row>
@@ -6101,7 +6098,7 @@
       <c r="A2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6127,7 +6124,9 @@
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -6175,7 +6174,7 @@
       <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="10"/>
+      <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -6247,7 +6246,9 @@
       <c r="A26" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="1"/>
+      <c r="B26" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19E8457-5C7E-4877-A907-5578DF95B7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067AFE0D-B9A8-4AB3-A78A-0D9AF8AA05EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="50">
   <si>
     <t>Alunos</t>
   </si>
@@ -185,6 +185,9 @@
   </si>
   <si>
     <t>Aula01-Proj Estacionamento</t>
+  </si>
+  <si>
+    <t>Ok</t>
   </si>
 </sst>
 </file>
@@ -1105,6 +1108,9 @@
       <c r="AV3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AW3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1251,6 +1257,9 @@
       <c r="AV4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AW4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1397,6 +1406,9 @@
       <c r="AV5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AW5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1543,6 +1555,9 @@
       <c r="AV6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AW6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1689,6 +1704,9 @@
       <c r="AV7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AW7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1835,6 +1853,9 @@
       <c r="AV8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AW8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1981,6 +2002,9 @@
       <c r="AV9" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AW9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2127,6 +2151,9 @@
       <c r="AV10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AW10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2273,6 +2300,9 @@
       <c r="AV11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AW11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2419,6 +2449,9 @@
       <c r="AV12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AW12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2565,6 +2598,9 @@
       <c r="AV13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AW13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -2711,6 +2747,9 @@
       <c r="AV14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AW14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -2857,6 +2896,9 @@
       <c r="AV15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AW15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3003,8 +3045,11 @@
       <c r="AV16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3149,8 +3194,11 @@
       <c r="AV17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3295,8 +3343,11 @@
       <c r="AV18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -3441,8 +3492,11 @@
       <c r="AV19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -3587,8 +3641,11 @@
       <c r="AV20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -3733,8 +3790,11 @@
       <c r="AV21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -3879,8 +3939,11 @@
       <c r="AV22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -4025,8 +4088,11 @@
       <c r="AV23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -4171,8 +4237,11 @@
       <c r="AV24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -4317,8 +4386,11 @@
       <c r="AV25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -4463,8 +4535,11 @@
       <c r="AV26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -4609,8 +4684,11 @@
       <c r="AV27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -4755,8 +4833,11 @@
       <c r="AV28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -4901,8 +4982,11 @@
       <c r="AV29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -5047,8 +5131,11 @@
       <c r="AV30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW30" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -5193,8 +5280,11 @@
       <c r="AV31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -5339,8 +5429,11 @@
       <c r="AV32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -5485,8 +5578,11 @@
       <c r="AV33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -5631,20 +5727,23 @@
       <c r="AV34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AW34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -6210,7 +6309,9 @@
       <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="1"/>
+      <c r="B20" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
@@ -6228,7 +6329,9 @@
       <c r="A23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -6280,13 +6383,17 @@
       <c r="A31" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="1"/>
+      <c r="B32" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067AFE0D-B9A8-4AB3-A78A-0D9AF8AA05EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B782784D-A102-4BFF-8580-23115B8D6375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="50">
   <si>
     <t>Alunos</t>
   </si>
@@ -6237,7 +6237,9 @@
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B782784D-A102-4BFF-8580-23115B8D6375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F45D1A-D9B1-4D76-9043-D372F1B48C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="50">
   <si>
     <t>Alunos</t>
   </si>
@@ -6299,7 +6299,9 @@
       <c r="A18" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="1"/>
+      <c r="B18" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F45D1A-D9B1-4D76-9043-D372F1B48C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18C7A51-A6CC-449A-A9D0-967D5A878153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="50">
   <si>
     <t>Alunos</t>
   </si>
@@ -175,9 +175,6 @@
     <t>Fernando Joaquim Mota</t>
   </si>
   <si>
-    <t>PP</t>
-  </si>
-  <si>
     <t>Aluno</t>
   </si>
   <si>
@@ -189,12 +186,15 @@
   <si>
     <t>Ok</t>
   </si>
+  <si>
+    <t>Aula03 Lanche e Quiz</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,6 +212,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -243,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -272,6 +280,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -805,6 +815,12 @@
       <c r="AW1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="AX1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -949,13 +965,17 @@
         <v>45875</v>
       </c>
       <c r="AV2" s="2">
-        <v>45876</v>
+        <v>45881</v>
       </c>
       <c r="AW2" s="2">
-        <v>45877</v>
-      </c>
-      <c r="AX2" s="2"/>
-      <c r="AY2" s="2"/>
+        <v>45882</v>
+      </c>
+      <c r="AX2" s="2">
+        <v>45888</v>
+      </c>
+      <c r="AY2" s="2">
+        <v>45889</v>
+      </c>
       <c r="AZ2" s="2"/>
       <c r="BA2" s="2"/>
       <c r="BB2" s="2"/>
@@ -1111,6 +1131,9 @@
       <c r="AW3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AX3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1260,6 +1283,9 @@
       <c r="AW4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AX4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1409,6 +1435,9 @@
       <c r="AW5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AX5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1558,6 +1587,9 @@
       <c r="AW6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AX6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1707,6 +1739,9 @@
       <c r="AW7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AX7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1856,6 +1891,9 @@
       <c r="AW8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AX8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2005,6 +2043,9 @@
       <c r="AW9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AX9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2154,6 +2195,9 @@
       <c r="AW10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AX10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2303,6 +2347,9 @@
       <c r="AW11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AX11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2452,6 +2499,9 @@
       <c r="AW12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AX12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2593,12 +2643,15 @@
         <v>3</v>
       </c>
       <c r="AU13" s="1" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="AV13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="AW13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AX13" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2750,6 +2803,9 @@
       <c r="AW14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AX14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -2899,6 +2955,9 @@
       <c r="AW15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AX15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3048,8 +3107,11 @@
       <c r="AW16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3197,8 +3259,11 @@
       <c r="AW17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3346,8 +3411,11 @@
       <c r="AW18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX18" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -3495,8 +3563,11 @@
       <c r="AW19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -3644,8 +3715,11 @@
       <c r="AW20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -3793,8 +3867,11 @@
       <c r="AW21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -3942,8 +4019,11 @@
       <c r="AW22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -4091,8 +4171,11 @@
       <c r="AW23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -4240,8 +4323,11 @@
       <c r="AW24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -4389,8 +4475,11 @@
       <c r="AW25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -4538,8 +4627,11 @@
       <c r="AW26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -4687,8 +4779,11 @@
       <c r="AW27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -4836,8 +4931,11 @@
       <c r="AW28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -4985,8 +5083,11 @@
       <c r="AW29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -5134,8 +5235,11 @@
       <c r="AW30" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -5283,8 +5387,11 @@
       <c r="AW31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -5432,8 +5539,11 @@
       <c r="AW32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -5581,8 +5691,11 @@
       <c r="AW33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -5730,20 +5843,23 @@
       <c r="AW34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:50" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:50" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:50" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:50" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -5754,7 +5870,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 AS1:XFD2 A3:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -6181,222 +6297,239 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82759A4A-CE41-47AD-9142-A6D90AD2CAA2}">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B1" s="8">
         <v>45875</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="C1" s="10">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="1"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>44</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="1"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="1"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="C26" s="11"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="C27" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>30</v>
       </c>
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18C7A51-A6CC-449A-A9D0-967D5A878153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68C46D4-EF60-4890-BDAD-FE8750E6BF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="50">
   <si>
     <t>Alunos</t>
   </si>
@@ -6349,6 +6349,9 @@
       <c r="B6" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="C6" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -6437,6 +6440,9 @@
         <v>19</v>
       </c>
       <c r="B19" s="1"/>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -6451,6 +6457,9 @@
         <v>21</v>
       </c>
       <c r="B21" s="1"/>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
@@ -6465,12 +6474,18 @@
       <c r="B23" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="1"/>
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
@@ -6509,6 +6524,9 @@
         <v>29</v>
       </c>
       <c r="B29" s="1"/>
+      <c r="C29" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
@@ -6529,6 +6547,9 @@
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" t="s">
         <v>48</v>
       </c>
     </row>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68C46D4-EF60-4890-BDAD-FE8750E6BF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA8C790-7679-4205-B0FC-9E9CB8A8C627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="50">
   <si>
     <t>Alunos</t>
   </si>
@@ -194,7 +194,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,14 +212,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -277,11 +269,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -672,11 +666,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
       <c r="D1" s="2" t="s">
         <v>35</v>
       </c>
@@ -1134,6 +1128,9 @@
       <c r="AX3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AY3" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="4" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1286,6 +1283,9 @@
       <c r="AX4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AY4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1438,6 +1438,9 @@
       <c r="AX5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AY5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1590,6 +1593,9 @@
       <c r="AX6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AY6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1742,6 +1748,9 @@
       <c r="AX7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AY7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1894,6 +1903,9 @@
       <c r="AX8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AY8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2046,6 +2058,9 @@
       <c r="AX9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AY9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2198,6 +2213,9 @@
       <c r="AX10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AY10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2350,6 +2368,9 @@
       <c r="AX11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AY11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2502,6 +2523,9 @@
       <c r="AX12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AY12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2654,6 +2678,9 @@
       <c r="AX13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AY13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -2806,6 +2833,9 @@
       <c r="AX14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AY14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -2958,6 +2988,9 @@
       <c r="AX15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AY15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3110,8 +3143,11 @@
       <c r="AX16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3262,8 +3298,11 @@
       <c r="AX17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3414,8 +3453,11 @@
       <c r="AX18" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -3566,8 +3608,11 @@
       <c r="AX19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -3718,8 +3763,11 @@
       <c r="AX20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -3870,8 +3918,11 @@
       <c r="AX21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -4022,8 +4073,11 @@
       <c r="AX22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -4174,8 +4228,11 @@
       <c r="AX23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -4326,8 +4383,11 @@
       <c r="AX24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -4478,8 +4538,11 @@
       <c r="AX25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -4630,8 +4693,11 @@
       <c r="AX26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -4782,8 +4848,11 @@
       <c r="AX27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -4934,8 +5003,11 @@
       <c r="AX28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -5086,8 +5158,11 @@
       <c r="AX29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -5238,8 +5313,11 @@
       <c r="AX30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -5390,8 +5468,11 @@
       <c r="AX31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -5542,8 +5623,11 @@
       <c r="AX32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -5694,8 +5778,11 @@
       <c r="AX33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -5846,20 +5933,23 @@
       <c r="AX34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -5870,7 +5960,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 AS1:XFD2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -6301,7 +6391,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6309,7 +6399,7 @@
       <c r="B1" s="8">
         <v>45875</v>
       </c>
-      <c r="C1" s="10">
+      <c r="C1" s="9">
         <v>45888</v>
       </c>
     </row>
@@ -6329,18 +6419,27 @@
         <v>5</v>
       </c>
       <c r="B3" s="1"/>
+      <c r="C3" s="11" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="1"/>
+      <c r="C4" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1"/>
+      <c r="C5" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -6349,7 +6448,7 @@
       <c r="B6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="11" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6358,6 +6457,9 @@
         <v>9</v>
       </c>
       <c r="B7" s="1"/>
+      <c r="C7" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -6366,37 +6468,50 @@
       <c r="B8" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="C8" s="11" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="1"/>
+      <c r="C9" s="11" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>44</v>
       </c>
       <c r="B10" s="1"/>
+      <c r="C10" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="1"/>
+      <c r="C11" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="1"/>
+      <c r="C12" s="11"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="1"/>
-      <c r="C13" t="s">
+      <c r="C13" s="11" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6405,7 +6520,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="1"/>
-      <c r="C14" t="s">
+      <c r="C14" s="11" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6414,18 +6529,25 @@
         <v>16</v>
       </c>
       <c r="B15" s="1"/>
+      <c r="C15" s="11"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="1"/>
+      <c r="C16" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="1"/>
+      <c r="C17" s="11" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -6434,13 +6556,14 @@
       <c r="B18" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="C18" s="11"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="1"/>
-      <c r="C19" t="s">
+      <c r="C19" s="11" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6451,13 +6574,16 @@
       <c r="B20" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="C20" s="11" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="1"/>
-      <c r="C21" t="s">
+      <c r="C21" s="11" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6466,6 +6592,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1"/>
+      <c r="C22" s="11"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
@@ -6474,7 +6601,7 @@
       <c r="B23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="11" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6483,7 +6610,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1"/>
-      <c r="C24" t="s">
+      <c r="C24" s="11" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6492,6 +6619,9 @@
         <v>25</v>
       </c>
       <c r="B25" s="1"/>
+      <c r="C25" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -6500,7 +6630,9 @@
       <c r="B26" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="11"/>
+      <c r="C26" s="11" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
@@ -6509,7 +6641,7 @@
       <c r="B27" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="11" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6518,13 +6650,14 @@
         <v>28</v>
       </c>
       <c r="B28" s="1"/>
+      <c r="C28" s="11"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B29" s="1"/>
-      <c r="C29" t="s">
+      <c r="C29" s="11" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6533,6 +6666,9 @@
         <v>30</v>
       </c>
       <c r="B30" s="1"/>
+      <c r="C30" s="11" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
@@ -6541,6 +6677,9 @@
       <c r="B31" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="C31" s="11" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -6549,21 +6688,23 @@
       <c r="B32" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B33" s="1"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C33" s="11"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B34" s="1"/>
+      <c r="C34" s="11"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3:A34">
@@ -6575,5 +6716,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA8C790-7679-4205-B0FC-9E9CB8A8C627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33167801-C4DA-4D68-83C2-CBE1E27F2718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1723" uniqueCount="50">
   <si>
     <t>Alunos</t>
   </si>
@@ -271,10 +271,10 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -666,11 +666,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
       <c r="D1" s="2" t="s">
         <v>35</v>
       </c>
@@ -6419,7 +6419,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1"/>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1"/>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6437,7 +6437,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
       <c r="B6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="1"/>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       <c r="B8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6477,7 +6477,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="1"/>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
         <v>44</v>
       </c>
       <c r="B10" s="1"/>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="1"/>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6504,14 +6504,14 @@
         <v>13</v>
       </c>
       <c r="B12" s="1"/>
-      <c r="C12" s="11"/>
+      <c r="C12" s="10"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="1"/>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="1"/>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6529,14 +6529,16 @@
         <v>16</v>
       </c>
       <c r="B15" s="1"/>
-      <c r="C15" s="11"/>
+      <c r="C15" s="10" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="1"/>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6545,7 +6547,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="1"/>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6556,14 +6558,14 @@
       <c r="B18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="11"/>
+      <c r="C18" s="10"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="1"/>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6574,7 +6576,7 @@
       <c r="B20" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6583,7 +6585,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1"/>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6592,7 +6594,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1"/>
-      <c r="C22" s="11"/>
+      <c r="C22" s="10"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
@@ -6601,7 +6603,7 @@
       <c r="B23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6610,7 +6612,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1"/>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6619,7 +6621,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1"/>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6630,7 +6632,7 @@
       <c r="B26" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6641,7 +6643,7 @@
       <c r="B27" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6650,14 +6652,14 @@
         <v>28</v>
       </c>
       <c r="B28" s="1"/>
-      <c r="C28" s="11"/>
+      <c r="C28" s="10"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B29" s="1"/>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6666,7 +6668,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1"/>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6677,7 +6679,7 @@
       <c r="B31" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6688,7 +6690,7 @@
       <c r="B32" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="10" t="s">
         <v>48</v>
       </c>
     </row>
@@ -6697,14 +6699,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="1"/>
-      <c r="C33" s="11"/>
+      <c r="C33" s="10"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B34" s="1"/>
-      <c r="C34" s="11"/>
+      <c r="C34" s="10" t="s">
+        <v>46</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3:A34">

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33167801-C4DA-4D68-83C2-CBE1E27F2718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFE1CCC-DAA7-41B7-AA55-B8A1367012C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1723" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="50">
   <si>
     <t>Alunos</t>
   </si>
@@ -815,6 +815,12 @@
       <c r="AY1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="AZ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -970,8 +976,12 @@
       <c r="AY2" s="2">
         <v>45889</v>
       </c>
-      <c r="AZ2" s="2"/>
-      <c r="BA2" s="2"/>
+      <c r="AZ2" s="2">
+        <v>45895</v>
+      </c>
+      <c r="BA2" s="2">
+        <v>45896</v>
+      </c>
       <c r="BB2" s="2"/>
       <c r="BC2" s="2"/>
       <c r="BD2" s="2"/>
@@ -1131,6 +1141,9 @@
       <c r="AY3" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="AZ3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1286,6 +1299,9 @@
       <c r="AY4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AZ4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1441,6 +1457,9 @@
       <c r="AY5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AZ5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1596,6 +1615,9 @@
       <c r="AY6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AZ6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1751,6 +1773,9 @@
       <c r="AY7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AZ7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1906,6 +1931,9 @@
       <c r="AY8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AZ8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2061,6 +2089,9 @@
       <c r="AY9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AZ9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2216,6 +2247,9 @@
       <c r="AY10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AZ10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2371,6 +2405,9 @@
       <c r="AY11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AZ11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2526,6 +2563,9 @@
       <c r="AY12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AZ12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2681,6 +2721,9 @@
       <c r="AY13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AZ13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -2836,6 +2879,9 @@
       <c r="AY14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AZ14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -2991,6 +3037,9 @@
       <c r="AY15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AZ15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3146,8 +3195,11 @@
       <c r="AY16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3301,8 +3353,11 @@
       <c r="AY17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3456,8 +3511,11 @@
       <c r="AY18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -3611,8 +3669,11 @@
       <c r="AY19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -3766,8 +3827,11 @@
       <c r="AY20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -3921,8 +3985,11 @@
       <c r="AY21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -4076,8 +4143,11 @@
       <c r="AY22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -4231,8 +4301,11 @@
       <c r="AY23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -4386,8 +4459,11 @@
       <c r="AY24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -4541,8 +4617,11 @@
       <c r="AY25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -4696,8 +4775,11 @@
       <c r="AY26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -4851,8 +4933,11 @@
       <c r="AY27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -5006,8 +5091,11 @@
       <c r="AY28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -5161,8 +5249,11 @@
       <c r="AY29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -5316,8 +5407,11 @@
       <c r="AY30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -5471,8 +5565,11 @@
       <c r="AY31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -5626,8 +5723,11 @@
       <c r="AY32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -5781,8 +5881,11 @@
       <c r="AY33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -5936,20 +6039,23 @@
       <c r="AY34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AZ34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -5960,7 +6066,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFE1CCC-DAA7-41B7-AA55-B8A1367012C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FBD5D2-0A5D-48F6-A05E-DBB062FCBCBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6066,7 +6066,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
+  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FBD5D2-0A5D-48F6-A05E-DBB062FCBCBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CA67FD-9344-44AB-BB32-CCF4FD3D5C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="54">
   <si>
     <t>Alunos</t>
   </si>
@@ -189,6 +189,18 @@
   <si>
     <t>Aula03 Lanche e Quiz</t>
   </si>
+  <si>
+    <t>Aula01 Semaforo</t>
+  </si>
+  <si>
+    <t>Projetos</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Iot</t>
+  </si>
 </sst>
 </file>
 
@@ -264,17 +276,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -666,11 +678,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
       <c r="D1" s="2" t="s">
         <v>35</v>
       </c>
@@ -6493,331 +6505,427 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82759A4A-CE41-47AD-9142-A6D90AD2CAA2}">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="8">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B1" s="9">
         <v>45875</v>
       </c>
-      <c r="C1" s="9">
+      <c r="C1" s="10">
         <v>45888</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="10">
+        <v>45895</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C3" s="11" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="D3" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="10" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="10" t="s">
+      <c r="B5" s="1"/>
+      <c r="C5" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="10" t="s">
+      <c r="B6" s="1"/>
+      <c r="C6" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C7" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="10" t="s">
+      <c r="B8" s="1"/>
+      <c r="C8" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="D8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C9" s="7" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="10" t="s">
+      <c r="B10" s="1"/>
+      <c r="C10" s="7" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="10" t="s">
+      <c r="B11" s="1"/>
+      <c r="C11" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="10" t="s">
+      <c r="B12" s="1"/>
+      <c r="C12" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="10"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="B13" s="1"/>
+      <c r="C13" s="7"/>
+      <c r="D13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="10" t="s">
+      <c r="B14" s="1"/>
+      <c r="C14" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="10" t="s">
+      <c r="B15" s="1"/>
+      <c r="C15" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="10" t="s">
+      <c r="B16" s="1"/>
+      <c r="C16" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="D16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="10" t="s">
+      <c r="B17" s="1"/>
+      <c r="C17" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="D17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="10" t="s">
+      <c r="B18" s="1"/>
+      <c r="C18" s="7" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="D18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="10"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="C19" s="7"/>
+      <c r="D19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="10" t="s">
+      <c r="B20" s="1"/>
+      <c r="C20" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="D20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C21" s="7" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="D21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="10" t="s">
+      <c r="B22" s="1"/>
+      <c r="C22" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="D22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="10"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="B23" s="1"/>
+      <c r="C23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C24" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="D24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="10" t="s">
+      <c r="B25" s="1"/>
+      <c r="C25" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="D25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="10" t="s">
+      <c r="B26" s="1"/>
+      <c r="C26" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="D26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="7" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="10"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="B29" s="1"/>
+      <c r="C29" s="7"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="10" t="s">
+      <c r="B30" s="1"/>
+      <c r="C30" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="D30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="10" t="s">
+      <c r="B31" s="1"/>
+      <c r="C31" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="10"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="B34" s="1"/>
+      <c r="C34" s="7"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="10" t="s">
+      <c r="B35" s="1"/>
+      <c r="C35" s="7" t="s">
         <v>46</v>
       </c>
+      <c r="D35" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A3:A34">
+  <conditionalFormatting sqref="A4:A35">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CA67FD-9344-44AB-BB32-CCF4FD3D5C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2D811F-1EC1-4F17-86BD-5ED357A6EF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -278,15 +278,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -678,11 +678,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
       <c r="D1" s="2" t="s">
         <v>35</v>
       </c>
@@ -6515,24 +6515,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B1" s="9">
+      <c r="B1" s="8">
         <v>45875</v>
       </c>
-      <c r="C1" s="10">
+      <c r="C1" s="9">
         <v>45888</v>
       </c>
-      <c r="D1" s="10">
+      <c r="D1" s="9">
         <v>45895</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>53</v>
       </c>
     </row>
@@ -6540,13 +6540,13 @@
       <c r="A3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>50</v>
       </c>
     </row>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2D811F-1EC1-4F17-86BD-5ED357A6EF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA1E4D5C-FB6C-4B15-B0C6-7D136E915555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="54">
   <si>
     <t>Alunos</t>
   </si>
@@ -833,6 +833,12 @@
       <c r="BA1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="BB1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -994,8 +1000,12 @@
       <c r="BA2" s="2">
         <v>45896</v>
       </c>
-      <c r="BB2" s="2"/>
-      <c r="BC2" s="2"/>
+      <c r="BB2" s="2">
+        <v>45902</v>
+      </c>
+      <c r="BC2" s="2">
+        <v>45903</v>
+      </c>
       <c r="BD2" s="2"/>
       <c r="BE2" s="2"/>
     </row>
@@ -1156,6 +1166,12 @@
       <c r="AZ3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BA3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1314,6 +1330,12 @@
       <c r="AZ4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BA4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1472,6 +1494,12 @@
       <c r="AZ5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BA5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1630,6 +1658,12 @@
       <c r="AZ6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BA6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1788,6 +1822,12 @@
       <c r="AZ7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BA7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1946,6 +1986,12 @@
       <c r="AZ8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BA8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2104,6 +2150,12 @@
       <c r="AZ9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BA9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2262,6 +2314,12 @@
       <c r="AZ10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BA10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2420,6 +2478,12 @@
       <c r="AZ11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BA11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2578,6 +2642,12 @@
       <c r="AZ12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BA12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2736,6 +2806,12 @@
       <c r="AZ13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BA13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -2894,6 +2970,12 @@
       <c r="AZ14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BA14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3052,6 +3134,12 @@
       <c r="AZ15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BA15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3210,8 +3298,14 @@
       <c r="AZ16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3368,8 +3462,14 @@
       <c r="AZ17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3526,8 +3626,14 @@
       <c r="AZ18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -3684,8 +3790,14 @@
       <c r="AZ19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -3842,8 +3954,14 @@
       <c r="AZ20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -4000,8 +4118,14 @@
       <c r="AZ21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -4158,8 +4282,14 @@
       <c r="AZ22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -4316,8 +4446,14 @@
       <c r="AZ23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -4474,8 +4610,14 @@
       <c r="AZ24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -4632,8 +4774,14 @@
       <c r="AZ25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -4790,8 +4938,14 @@
       <c r="AZ26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -4948,8 +5102,14 @@
       <c r="AZ27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -5106,8 +5266,14 @@
       <c r="AZ28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -5264,8 +5430,14 @@
       <c r="AZ29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -5422,8 +5594,14 @@
       <c r="AZ30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -5580,8 +5758,14 @@
       <c r="AZ31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -5738,8 +5922,14 @@
       <c r="AZ32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -5896,8 +6086,14 @@
       <c r="AZ33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -6054,20 +6250,26 @@
       <c r="AZ34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BA34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:54" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:54" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:54" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:54" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:54" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -6078,7 +6280,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 AS1:XFD2 A3:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA1E4D5C-FB6C-4B15-B0C6-7D136E915555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576733FC-D600-4416-A8A4-FCE8E4BF2D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="54">
   <si>
     <t>Alunos</t>
   </si>
@@ -839,6 +839,12 @@
       <c r="BC1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="BD1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1006,8 +1012,12 @@
       <c r="BC2" s="2">
         <v>45903</v>
       </c>
-      <c r="BD2" s="2"/>
-      <c r="BE2" s="2"/>
+      <c r="BD2" s="2">
+        <v>45909</v>
+      </c>
+      <c r="BE2" s="2">
+        <v>45910</v>
+      </c>
     </row>
     <row r="3" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
@@ -1172,6 +1182,9 @@
       <c r="BB3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BC3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1336,6 +1349,9 @@
       <c r="BB4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BC4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1500,6 +1516,9 @@
       <c r="BB5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BC5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1664,6 +1683,9 @@
       <c r="BB6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BC6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1828,6 +1850,9 @@
       <c r="BB7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BC7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1992,6 +2017,9 @@
       <c r="BB8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BC8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2156,6 +2184,9 @@
       <c r="BB9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BC9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2320,6 +2351,9 @@
       <c r="BB10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BC10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2484,6 +2518,9 @@
       <c r="BB11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BC11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2648,6 +2685,9 @@
       <c r="BB12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BC12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2812,6 +2852,9 @@
       <c r="BB13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BC13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -2976,6 +3019,9 @@
       <c r="BB14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BC14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3140,6 +3186,9 @@
       <c r="BB15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BC15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3304,8 +3353,11 @@
       <c r="BB16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3468,8 +3520,11 @@
       <c r="BB17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3632,8 +3687,11 @@
       <c r="BB18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -3796,8 +3854,11 @@
       <c r="BB19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -3960,8 +4021,11 @@
       <c r="BB20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -4124,8 +4188,11 @@
       <c r="BB21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -4288,8 +4355,11 @@
       <c r="BB22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -4452,8 +4522,11 @@
       <c r="BB23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -4616,8 +4689,11 @@
       <c r="BB24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -4780,8 +4856,11 @@
       <c r="BB25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -4944,8 +5023,11 @@
       <c r="BB26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -5108,8 +5190,11 @@
       <c r="BB27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -5272,8 +5357,11 @@
       <c r="BB28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -5436,8 +5524,11 @@
       <c r="BB29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -5600,8 +5691,11 @@
       <c r="BB30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -5764,8 +5858,11 @@
       <c r="BB31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -5928,8 +6025,11 @@
       <c r="BB32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -6092,8 +6192,11 @@
       <c r="BB33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -6256,20 +6359,23 @@
       <c r="BB34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:55" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:55" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:55" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:55" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:55" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -6280,7 +6386,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 AS1:XFD2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576733FC-D600-4416-A8A4-FCE8E4BF2D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A9A35C-D3BC-4B86-8197-9DAC2A55D986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="54">
   <si>
     <t>Alunos</t>
   </si>
@@ -1185,6 +1185,9 @@
       <c r="BC3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BD3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1352,6 +1355,9 @@
       <c r="BC4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BD4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1519,6 +1525,9 @@
       <c r="BC5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BD5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1686,6 +1695,9 @@
       <c r="BC6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BD6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1853,6 +1865,9 @@
       <c r="BC7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BD7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2020,6 +2035,9 @@
       <c r="BC8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BD8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2187,6 +2205,9 @@
       <c r="BC9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BD9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2354,6 +2375,9 @@
       <c r="BC10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BD10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2521,6 +2545,9 @@
       <c r="BC11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BD11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2688,6 +2715,9 @@
       <c r="BC12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BD12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2855,6 +2885,9 @@
       <c r="BC13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BD13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3022,6 +3055,9 @@
       <c r="BC14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BD14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3189,6 +3225,9 @@
       <c r="BC15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BD15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3356,8 +3395,11 @@
       <c r="BC16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3523,8 +3565,11 @@
       <c r="BC17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3690,8 +3735,11 @@
       <c r="BC18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -3857,8 +3905,11 @@
       <c r="BC19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -4024,8 +4075,11 @@
       <c r="BC20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -4191,8 +4245,11 @@
       <c r="BC21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -4358,8 +4415,11 @@
       <c r="BC22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -4525,8 +4585,11 @@
       <c r="BC23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -4692,8 +4755,11 @@
       <c r="BC24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -4859,8 +4925,11 @@
       <c r="BC25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -5026,8 +5095,11 @@
       <c r="BC26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -5193,8 +5265,11 @@
       <c r="BC27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -5360,8 +5435,11 @@
       <c r="BC28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -5527,8 +5605,11 @@
       <c r="BC29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -5694,8 +5775,11 @@
       <c r="BC30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -5861,8 +5945,11 @@
       <c r="BC31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -6028,8 +6115,11 @@
       <c r="BC32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -6195,8 +6285,11 @@
       <c r="BC33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -6362,20 +6455,23 @@
       <c r="BC34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="BD34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:56" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:56" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:56" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:56" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:56" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A9A35C-D3BC-4B86-8197-9DAC2A55D986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7E3DFE-6DC6-405F-A8B3-73A5D0EC254F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="54">
   <si>
     <t>Alunos</t>
   </si>
@@ -1188,6 +1188,9 @@
       <c r="BD3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BE3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1358,6 +1361,9 @@
       <c r="BD4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BE4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1528,6 +1534,9 @@
       <c r="BD5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BE5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1698,6 +1707,9 @@
       <c r="BD6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BE6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1868,6 +1880,9 @@
       <c r="BD7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BE7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2038,6 +2053,9 @@
       <c r="BD8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BE8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2208,6 +2226,9 @@
       <c r="BD9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BE9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2378,6 +2399,9 @@
       <c r="BD10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BE10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2548,6 +2572,9 @@
       <c r="BD11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BE11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2718,6 +2745,9 @@
       <c r="BD12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BE12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2888,6 +2918,9 @@
       <c r="BD13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BE13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3058,6 +3091,9 @@
       <c r="BD14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BE14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3228,6 +3264,9 @@
       <c r="BD15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BE15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3398,8 +3437,11 @@
       <c r="BD16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3568,8 +3610,11 @@
       <c r="BD17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3738,8 +3783,11 @@
       <c r="BD18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -3908,8 +3956,11 @@
       <c r="BD19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -4078,8 +4129,11 @@
       <c r="BD20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -4248,8 +4302,11 @@
       <c r="BD21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -4418,8 +4475,11 @@
       <c r="BD22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -4588,8 +4648,11 @@
       <c r="BD23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -4758,8 +4821,11 @@
       <c r="BD24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -4928,8 +4994,11 @@
       <c r="BD25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -5098,8 +5167,11 @@
       <c r="BD26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -5268,8 +5340,11 @@
       <c r="BD27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -5438,8 +5513,11 @@
       <c r="BD28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -5608,8 +5686,11 @@
       <c r="BD29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -5778,8 +5859,11 @@
       <c r="BD30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE30" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -5948,8 +6032,11 @@
       <c r="BD31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -6118,8 +6205,11 @@
       <c r="BD32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -6288,8 +6378,11 @@
       <c r="BD33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -6458,20 +6551,23 @@
       <c r="BD34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="BE34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:57" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:57" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:57" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:57" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:57" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7E3DFE-6DC6-405F-A8B3-73A5D0EC254F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464C634B-A09D-49F9-A9C5-03D2CA33CE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="55">
   <si>
     <t>Alunos</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>Iot</t>
+  </si>
+  <si>
+    <t>2P</t>
   </si>
 </sst>
 </file>
@@ -658,7 +661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BE39"/>
+  <dimension ref="A1:CE39"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -674,10 +677,11 @@
     <col min="44" max="44" width="6.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="46" max="57" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="16384" width="6.7109375" style="1"/>
+    <col min="58" max="58" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -845,8 +849,14 @@
       <c r="BE1" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
@@ -1018,8 +1028,38 @@
       <c r="BE2" s="2">
         <v>45910</v>
       </c>
-    </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF2" s="2">
+        <v>45911</v>
+      </c>
+      <c r="BG2" s="2">
+        <v>45912</v>
+      </c>
+      <c r="BH2" s="2"/>
+      <c r="BI2" s="2"/>
+      <c r="BJ2" s="2"/>
+      <c r="BK2" s="2"/>
+      <c r="BL2" s="2"/>
+      <c r="BM2" s="2"/>
+      <c r="BN2" s="2"/>
+      <c r="BO2" s="2"/>
+      <c r="BP2" s="2"/>
+      <c r="BQ2" s="2"/>
+      <c r="BR2" s="2"/>
+      <c r="BS2" s="2"/>
+      <c r="BT2" s="2"/>
+      <c r="BU2" s="2"/>
+      <c r="BV2" s="2"/>
+      <c r="BW2" s="2"/>
+      <c r="BX2" s="2"/>
+      <c r="BY2" s="2"/>
+      <c r="BZ2" s="2"/>
+      <c r="CA2" s="2"/>
+      <c r="CB2" s="2"/>
+      <c r="CC2" s="2"/>
+      <c r="CD2" s="2"/>
+      <c r="CE2" s="2"/>
+    </row>
+    <row r="3" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>24126008</v>
       </c>
@@ -1191,8 +1231,11 @@
       <c r="BE3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>24125990</v>
       </c>
@@ -1364,8 +1407,11 @@
       <c r="BE4" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>24125969</v>
       </c>
@@ -1537,8 +1583,11 @@
       <c r="BE5" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>24125996</v>
       </c>
@@ -1710,8 +1759,11 @@
       <c r="BE6" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF6" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>24125975</v>
       </c>
@@ -1883,8 +1935,11 @@
       <c r="BE7" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF7" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>24125978</v>
       </c>
@@ -2056,8 +2111,11 @@
       <c r="BE8" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF8" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>24125993</v>
       </c>
@@ -2229,8 +2287,11 @@
       <c r="BE9" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF9" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>24126043</v>
       </c>
@@ -2402,8 +2463,11 @@
       <c r="BE10" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF10" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>24125985</v>
       </c>
@@ -2575,8 +2639,11 @@
       <c r="BE11" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF11" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>24125984</v>
       </c>
@@ -2748,8 +2815,11 @@
       <c r="BE12" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF12" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>24125988</v>
       </c>
@@ -2921,8 +2991,11 @@
       <c r="BE13" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF13" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>24126459</v>
       </c>
@@ -3094,8 +3167,11 @@
       <c r="BE14" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF14" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>24126094</v>
       </c>
@@ -3267,8 +3343,11 @@
       <c r="BE15" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF15" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>24126041</v>
       </c>
@@ -3440,8 +3519,11 @@
       <c r="BE16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3613,8 +3695,11 @@
       <c r="BE17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3786,8 +3871,11 @@
       <c r="BE18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -3959,8 +4047,11 @@
       <c r="BE19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -4132,8 +4223,11 @@
       <c r="BE20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -4305,8 +4399,11 @@
       <c r="BE21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -4478,8 +4575,11 @@
       <c r="BE22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -4651,8 +4751,11 @@
       <c r="BE23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -4824,8 +4927,11 @@
       <c r="BE24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -4997,8 +5103,11 @@
       <c r="BE25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -5170,8 +5279,11 @@
       <c r="BE26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -5343,8 +5455,11 @@
       <c r="BE27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -5516,8 +5631,11 @@
       <c r="BE28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF28" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -5689,8 +5807,11 @@
       <c r="BE29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -5862,8 +5983,11 @@
       <c r="BE30" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -6035,8 +6159,11 @@
       <c r="BE31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -6208,8 +6335,11 @@
       <c r="BE32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -6381,8 +6511,11 @@
       <c r="BE33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -6554,20 +6687,23 @@
       <c r="BE34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BF34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:58" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:58" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:58" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:58" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:58" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -6578,7 +6714,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464C634B-A09D-49F9-A9C5-03D2CA33CE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA49E99-F909-48E1-B809-89257B590A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2017" uniqueCount="55">
   <si>
     <t>Alunos</t>
   </si>
@@ -1029,10 +1029,10 @@
         <v>45910</v>
       </c>
       <c r="BF2" s="2">
-        <v>45911</v>
+        <v>45916</v>
       </c>
       <c r="BG2" s="2">
-        <v>45912</v>
+        <v>45917</v>
       </c>
       <c r="BH2" s="2"/>
       <c r="BI2" s="2"/>
@@ -1234,6 +1234,9 @@
       <c r="BF3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BG3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1410,6 +1413,9 @@
       <c r="BF4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BG4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1586,6 +1592,9 @@
       <c r="BF5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BG5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1762,6 +1771,9 @@
       <c r="BF6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BG6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1938,6 +1950,9 @@
       <c r="BF7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BG7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2114,6 +2129,9 @@
       <c r="BF8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BG8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2290,6 +2308,9 @@
       <c r="BF9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BG9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2466,6 +2487,9 @@
       <c r="BF10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BG10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2642,6 +2666,9 @@
       <c r="BF11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BG11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2818,6 +2845,9 @@
       <c r="BF12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BG12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2994,6 +3024,9 @@
       <c r="BF13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BG13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3170,6 +3203,9 @@
       <c r="BF14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BG14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3346,6 +3382,9 @@
       <c r="BF15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BG15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3522,8 +3561,11 @@
       <c r="BF16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3698,8 +3740,11 @@
       <c r="BF17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3874,8 +3919,11 @@
       <c r="BF18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -4050,8 +4098,11 @@
       <c r="BF19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -4226,8 +4277,11 @@
       <c r="BF20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -4402,8 +4456,11 @@
       <c r="BF21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -4578,8 +4635,11 @@
       <c r="BF22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -4754,8 +4814,11 @@
       <c r="BF23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -4930,8 +4993,11 @@
       <c r="BF24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -5106,8 +5172,11 @@
       <c r="BF25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -5282,8 +5351,11 @@
       <c r="BF26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -5458,8 +5530,11 @@
       <c r="BF27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -5634,8 +5709,11 @@
       <c r="BF28" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="29" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -5810,8 +5888,11 @@
       <c r="BF29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -5986,8 +6067,11 @@
       <c r="BF30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -6162,8 +6246,11 @@
       <c r="BF31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -6338,8 +6425,11 @@
       <c r="BF32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -6514,8 +6604,11 @@
       <c r="BF33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -6690,20 +6783,23 @@
       <c r="BF34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:59" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:59" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:59" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:59" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:59" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA49E99-F909-48E1-B809-89257B590A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16F5F31-D36C-416A-82CF-E0348BFFDFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2017" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="55">
   <si>
     <t>Alunos</t>
   </si>
@@ -855,6 +855,12 @@
       <c r="BG1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="BH1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1034,8 +1040,12 @@
       <c r="BG2" s="2">
         <v>45917</v>
       </c>
-      <c r="BH2" s="2"/>
-      <c r="BI2" s="2"/>
+      <c r="BH2" s="2">
+        <v>45923</v>
+      </c>
+      <c r="BI2" s="2">
+        <v>45924</v>
+      </c>
       <c r="BJ2" s="2"/>
       <c r="BK2" s="2"/>
       <c r="BL2" s="2"/>
@@ -1237,6 +1247,9 @@
       <c r="BG3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BH3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1416,6 +1429,9 @@
       <c r="BG4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BH4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1595,6 +1611,9 @@
       <c r="BG5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BH5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1774,6 +1793,9 @@
       <c r="BG6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BH6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1953,6 +1975,9 @@
       <c r="BG7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BH7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2132,6 +2157,9 @@
       <c r="BG8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BH8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2311,6 +2339,9 @@
       <c r="BG9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BH9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2490,6 +2521,9 @@
       <c r="BG10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BH10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2669,6 +2703,9 @@
       <c r="BG11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BH11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2848,6 +2885,9 @@
       <c r="BG12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BH12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3027,6 +3067,9 @@
       <c r="BG13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BH13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3206,6 +3249,9 @@
       <c r="BG14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BH14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3385,6 +3431,9 @@
       <c r="BG15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BH15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3564,8 +3613,11 @@
       <c r="BG16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3743,8 +3795,11 @@
       <c r="BG17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3922,8 +3977,11 @@
       <c r="BG18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -4101,8 +4159,11 @@
       <c r="BG19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -4280,8 +4341,11 @@
       <c r="BG20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -4459,8 +4523,11 @@
       <c r="BG21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -4638,8 +4705,11 @@
       <c r="BG22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -4817,8 +4887,11 @@
       <c r="BG23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -4996,8 +5069,11 @@
       <c r="BG24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -5175,8 +5251,11 @@
       <c r="BG25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -5354,8 +5433,11 @@
       <c r="BG26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -5533,8 +5615,11 @@
       <c r="BG27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -5712,8 +5797,11 @@
       <c r="BG28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -5891,8 +5979,11 @@
       <c r="BG29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -6070,8 +6161,11 @@
       <c r="BG30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -6249,8 +6343,11 @@
       <c r="BG31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -6428,8 +6525,11 @@
       <c r="BG32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -6607,8 +6707,11 @@
       <c r="BG33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -6786,20 +6889,23 @@
       <c r="BG34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BH34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:60" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:60" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:60" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:60" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:60" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisf\Documents\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16F5F31-D36C-416A-82CF-E0348BFFDFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8D7F7F-5C25-4B88-B3D5-E21B2922CFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -22,23 +22,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="55">
   <si>
     <t>Alunos</t>
   </si>
@@ -365,9 +354,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -405,7 +394,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -511,7 +500,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -653,7 +642,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1250,6 +1239,9 @@
       <c r="BH3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BI3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1432,6 +1424,9 @@
       <c r="BH4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BI4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1614,6 +1609,9 @@
       <c r="BH5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BI5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1796,6 +1794,9 @@
       <c r="BH6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BI6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1978,6 +1979,9 @@
       <c r="BH7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BI7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2160,6 +2164,9 @@
       <c r="BH8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BI8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2342,6 +2349,9 @@
       <c r="BH9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BI9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2524,6 +2534,9 @@
       <c r="BH10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BI10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2706,6 +2719,9 @@
       <c r="BH11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BI11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2888,6 +2904,9 @@
       <c r="BH12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BI12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3070,6 +3089,9 @@
       <c r="BH13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BI13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3252,6 +3274,9 @@
       <c r="BH14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BI14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3434,6 +3459,9 @@
       <c r="BH15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BI15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3616,8 +3644,11 @@
       <c r="BH16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3798,8 +3829,11 @@
       <c r="BH17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -3980,8 +4014,11 @@
       <c r="BH18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -4162,8 +4199,11 @@
       <c r="BH19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -4344,8 +4384,11 @@
       <c r="BH20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -4526,8 +4569,11 @@
       <c r="BH21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -4708,8 +4754,11 @@
       <c r="BH22" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -4890,8 +4939,11 @@
       <c r="BH23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -5072,8 +5124,11 @@
       <c r="BH24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -5254,8 +5309,11 @@
       <c r="BH25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -5436,8 +5494,11 @@
       <c r="BH26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -5618,8 +5679,11 @@
       <c r="BH27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -5800,8 +5864,11 @@
       <c r="BH28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -5982,8 +6049,11 @@
       <c r="BH29" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -6164,8 +6234,11 @@
       <c r="BH30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -6346,8 +6419,11 @@
       <c r="BH31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -6528,8 +6604,11 @@
       <c r="BH32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -6710,8 +6789,11 @@
       <c r="BH33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -6892,20 +6974,23 @@
       <c r="BH34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="BI34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:61" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:61" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:61" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:61" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:61" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -6916,7 +7001,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
+  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisf\Documents\wellifabio\senai2025\ds\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8D7F7F-5C25-4B88-B3D5-E21B2922CFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96ADE12B-57C9-4ADA-A921-89EF94595E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3870" yWindow="1035" windowWidth="17670" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -354,9 +365,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -394,7 +405,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -500,7 +511,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -642,7 +653,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6047,10 +6058,10 @@
         <v>3</v>
       </c>
       <c r="BH29" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="BI29" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:61" x14ac:dyDescent="0.25">

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96ADE12B-57C9-4ADA-A921-89EF94595E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17970F3-483E-4D22-A0F5-C6243A964952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3870" yWindow="1035" windowWidth="17670" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="55">
   <si>
     <t>Alunos</t>
   </si>
@@ -861,6 +861,9 @@
       <c r="BI1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="BJ1" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="2" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1046,7 +1049,9 @@
       <c r="BI2" s="2">
         <v>45924</v>
       </c>
-      <c r="BJ2" s="2"/>
+      <c r="BJ2" s="2">
+        <v>45930</v>
+      </c>
       <c r="BK2" s="2"/>
       <c r="BL2" s="2"/>
       <c r="BM2" s="2"/>
@@ -1253,6 +1258,9 @@
       <c r="BI3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BJ3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1438,6 +1446,9 @@
       <c r="BI4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BJ4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1623,6 +1634,9 @@
       <c r="BI5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BJ5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1808,6 +1822,9 @@
       <c r="BI6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BJ6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1993,6 +2010,9 @@
       <c r="BI7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BJ7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2178,6 +2198,9 @@
       <c r="BI8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BJ8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2363,6 +2386,9 @@
       <c r="BI9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BJ9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2548,6 +2574,9 @@
       <c r="BI10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BJ10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2733,6 +2762,9 @@
       <c r="BI11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BJ11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2918,6 +2950,9 @@
       <c r="BI12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BJ12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3103,6 +3138,9 @@
       <c r="BI13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BJ13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3288,6 +3326,9 @@
       <c r="BI14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BJ14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3473,6 +3514,9 @@
       <c r="BI15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BJ15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3658,8 +3702,11 @@
       <c r="BI16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3843,8 +3890,11 @@
       <c r="BI17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -4028,8 +4078,11 @@
       <c r="BI18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -4213,8 +4266,11 @@
       <c r="BI19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -4398,8 +4454,11 @@
       <c r="BI20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -4583,8 +4642,11 @@
       <c r="BI21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -4768,8 +4830,11 @@
       <c r="BI22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -4953,8 +5018,11 @@
       <c r="BI23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -5138,8 +5206,11 @@
       <c r="BI24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -5323,8 +5394,11 @@
       <c r="BI25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -5508,8 +5582,11 @@
       <c r="BI26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -5693,8 +5770,11 @@
       <c r="BI27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -5878,8 +5958,11 @@
       <c r="BI28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -6063,8 +6146,11 @@
       <c r="BI29" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="30" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ29" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -6248,8 +6334,11 @@
       <c r="BI30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -6433,8 +6522,11 @@
       <c r="BI31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -6618,8 +6710,11 @@
       <c r="BI32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -6803,8 +6898,11 @@
       <c r="BI33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -6988,20 +7086,23 @@
       <c r="BI34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="BJ34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:62" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:62" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:62" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:62" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:62" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17970F3-483E-4D22-A0F5-C6243A964952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C82307-77D6-4853-BDDC-B6CD8A4A6443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2181" uniqueCount="55">
   <si>
     <t>Alunos</t>
   </si>
@@ -864,6 +864,9 @@
       <c r="BJ1" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="BK1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1052,9 +1055,15 @@
       <c r="BJ2" s="2">
         <v>45930</v>
       </c>
-      <c r="BK2" s="2"/>
-      <c r="BL2" s="2"/>
-      <c r="BM2" s="2"/>
+      <c r="BK2" s="2">
+        <v>45931</v>
+      </c>
+      <c r="BL2" s="2">
+        <v>45937</v>
+      </c>
+      <c r="BM2" s="2">
+        <v>45938</v>
+      </c>
       <c r="BN2" s="2"/>
       <c r="BO2" s="2"/>
       <c r="BP2" s="2"/>
@@ -1261,6 +1270,12 @@
       <c r="BJ3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BK3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1449,6 +1464,12 @@
       <c r="BJ4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BK4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1637,6 +1658,12 @@
       <c r="BJ5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BK5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1825,6 +1852,12 @@
       <c r="BJ6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BK6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2013,6 +2046,12 @@
       <c r="BJ7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BK7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2201,6 +2240,12 @@
       <c r="BJ8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BK8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2389,6 +2434,12 @@
       <c r="BJ9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BK9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2577,6 +2628,12 @@
       <c r="BJ10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BK10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2765,6 +2822,12 @@
       <c r="BJ11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BK11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -2953,6 +3016,12 @@
       <c r="BJ12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BK12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3141,6 +3210,12 @@
       <c r="BJ13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BK13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3329,6 +3404,12 @@
       <c r="BJ14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BK14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3517,6 +3598,12 @@
       <c r="BJ15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BK15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3705,8 +3792,14 @@
       <c r="BJ16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3893,8 +3986,14 @@
       <c r="BJ17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -4081,8 +4180,14 @@
       <c r="BJ18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -4269,8 +4374,14 @@
       <c r="BJ19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -4457,8 +4568,14 @@
       <c r="BJ20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -4645,8 +4762,14 @@
       <c r="BJ21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -4833,8 +4956,14 @@
       <c r="BJ22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -5021,8 +5150,14 @@
       <c r="BJ23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -5209,8 +5344,14 @@
       <c r="BJ24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -5397,8 +5538,14 @@
       <c r="BJ25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BL25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -5585,8 +5732,14 @@
       <c r="BJ26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -5773,8 +5926,14 @@
       <c r="BJ27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -5961,8 +6120,14 @@
       <c r="BJ28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -6149,8 +6314,14 @@
       <c r="BJ29" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="30" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -6337,8 +6508,14 @@
       <c r="BJ30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -6525,8 +6702,14 @@
       <c r="BJ31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -6713,8 +6896,14 @@
       <c r="BJ32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -6901,8 +7090,14 @@
       <c r="BJ33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -7089,20 +7284,26 @@
       <c r="BJ34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BK34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BL34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:64" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:64" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:64" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:64" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:64" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -7113,7 +7314,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 AS1:XFD2 A3:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C82307-77D6-4853-BDDC-B6CD8A4A6443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4325342-C385-4292-9D00-DF229ED7263C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2181" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2249" uniqueCount="55">
   <si>
     <t>Alunos</t>
   </si>
@@ -867,6 +867,18 @@
       <c r="BK1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="BL1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1064,8 +1076,12 @@
       <c r="BM2" s="2">
         <v>45938</v>
       </c>
-      <c r="BN2" s="2"/>
-      <c r="BO2" s="2"/>
+      <c r="BN2" s="2">
+        <v>45944</v>
+      </c>
+      <c r="BO2" s="2">
+        <v>45945</v>
+      </c>
       <c r="BP2" s="2"/>
       <c r="BQ2" s="2"/>
       <c r="BR2" s="2"/>
@@ -1276,6 +1292,12 @@
       <c r="BL3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BM3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1470,6 +1492,12 @@
       <c r="BL4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BM4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1664,6 +1692,12 @@
       <c r="BL5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BM5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1858,6 +1892,12 @@
       <c r="BL6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BM6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN6" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2052,6 +2092,12 @@
       <c r="BL7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BM7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2246,6 +2292,12 @@
       <c r="BL8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BM8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2440,6 +2492,12 @@
       <c r="BL9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BM9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2634,6 +2692,12 @@
       <c r="BL10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BM10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2828,6 +2892,12 @@
       <c r="BL11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BM11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3022,6 +3092,12 @@
       <c r="BL12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BM12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3216,6 +3292,12 @@
       <c r="BL13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BM13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3410,6 +3492,12 @@
       <c r="BL14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BM14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN14" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3604,6 +3692,12 @@
       <c r="BL15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BM15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3798,8 +3892,14 @@
       <c r="BL16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -3992,8 +4092,14 @@
       <c r="BL17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -4186,8 +4292,14 @@
       <c r="BL18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN18" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -4380,8 +4492,14 @@
       <c r="BL19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -4574,8 +4692,14 @@
       <c r="BL20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -4768,8 +4892,14 @@
       <c r="BL21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -4962,8 +5092,14 @@
       <c r="BL22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -5156,8 +5292,14 @@
       <c r="BL23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -5350,8 +5492,14 @@
       <c r="BL24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -5544,8 +5692,14 @@
       <c r="BL25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -5738,8 +5892,14 @@
       <c r="BL26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -5932,8 +6092,14 @@
       <c r="BL27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -6126,8 +6292,14 @@
       <c r="BL28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -6320,8 +6492,14 @@
       <c r="BL29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -6514,8 +6692,14 @@
       <c r="BL30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -6708,8 +6892,14 @@
       <c r="BL31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -6902,8 +7092,14 @@
       <c r="BL32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -7096,8 +7292,14 @@
       <c r="BL33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -7290,20 +7492,26 @@
       <c r="BL34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="BM34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:66" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:66" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:66" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:66" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:66" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -7314,7 +7522,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 AS1:XFD2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4325342-C385-4292-9D00-DF229ED7263C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610391AD-B26C-47DB-9EB7-86E216A80300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2249" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2281" uniqueCount="55">
   <si>
     <t>Alunos</t>
   </si>
@@ -1298,6 +1298,9 @@
       <c r="BN3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BO3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1498,6 +1501,9 @@
       <c r="BN4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BO4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1698,6 +1704,9 @@
       <c r="BN5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BO5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1898,6 +1907,9 @@
       <c r="BN6" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="BO6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2098,6 +2110,9 @@
       <c r="BN7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BO7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2298,6 +2313,9 @@
       <c r="BN8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BO8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2498,6 +2516,9 @@
       <c r="BN9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BO9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2698,6 +2719,9 @@
       <c r="BN10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BO10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2898,6 +2922,9 @@
       <c r="BN11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BO11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3098,6 +3125,9 @@
       <c r="BN12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BO12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3298,6 +3328,9 @@
       <c r="BN13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BO13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3498,6 +3531,9 @@
       <c r="BN14" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="BO14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3698,6 +3734,9 @@
       <c r="BN15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BO15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3898,8 +3937,11 @@
       <c r="BN16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -4098,8 +4140,11 @@
       <c r="BN17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -4298,8 +4343,11 @@
       <c r="BN18" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -4498,8 +4546,11 @@
       <c r="BN19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -4698,8 +4749,11 @@
       <c r="BN20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -4898,8 +4952,11 @@
       <c r="BN21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -5098,8 +5155,11 @@
       <c r="BN22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -5298,8 +5358,11 @@
       <c r="BN23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -5498,8 +5561,11 @@
       <c r="BN24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -5698,8 +5764,11 @@
       <c r="BN25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -5898,8 +5967,11 @@
       <c r="BN26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -6098,8 +6170,11 @@
       <c r="BN27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -6298,8 +6373,11 @@
       <c r="BN28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -6498,8 +6576,11 @@
       <c r="BN29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -6698,8 +6779,11 @@
       <c r="BN30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -6898,8 +6982,11 @@
       <c r="BN31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -7098,8 +7185,11 @@
       <c r="BN32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -7298,8 +7388,11 @@
       <c r="BN33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -7498,20 +7591,23 @@
       <c r="BN34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="BO34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:67" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:67" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:67" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:67" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:67" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -7522,7 +7618,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
+  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610391AD-B26C-47DB-9EB7-86E216A80300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2DA3A6-C86A-434C-AB6E-20EDB92D3DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1905,7 +1905,7 @@
         <v>3</v>
       </c>
       <c r="BN6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO6" s="1" t="s">
         <v>3</v>
@@ -3529,7 +3529,7 @@
         <v>3</v>
       </c>
       <c r="BN14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO14" s="1" t="s">
         <v>3</v>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2DA3A6-C86A-434C-AB6E-20EDB92D3DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E29950-B8AE-4925-B227-CCD0E2F526BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2281" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="55">
   <si>
     <t>Alunos</t>
   </si>
@@ -879,6 +879,12 @@
       <c r="BO1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="BP1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1082,8 +1088,12 @@
       <c r="BO2" s="2">
         <v>45945</v>
       </c>
-      <c r="BP2" s="2"/>
-      <c r="BQ2" s="2"/>
+      <c r="BP2" s="2">
+        <v>45951</v>
+      </c>
+      <c r="BQ2" s="2">
+        <v>45952</v>
+      </c>
       <c r="BR2" s="2"/>
       <c r="BS2" s="2"/>
       <c r="BT2" s="2"/>
@@ -1301,6 +1311,9 @@
       <c r="BO3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BP3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1504,6 +1517,9 @@
       <c r="BO4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BP4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1707,6 +1723,9 @@
       <c r="BO5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BP5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1910,6 +1929,9 @@
       <c r="BO6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BP6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2113,6 +2135,9 @@
       <c r="BO7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BP7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2316,6 +2341,9 @@
       <c r="BO8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BP8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2519,6 +2547,9 @@
       <c r="BO9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BP9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2722,6 +2753,9 @@
       <c r="BO10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BP10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2925,6 +2959,9 @@
       <c r="BO11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BP11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3128,6 +3165,9 @@
       <c r="BO12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BP12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3331,6 +3371,9 @@
       <c r="BO13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BP13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3534,6 +3577,9 @@
       <c r="BO14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BP14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3737,6 +3783,9 @@
       <c r="BO15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BP15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3940,8 +3989,11 @@
       <c r="BO16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -4143,8 +4195,11 @@
       <c r="BO17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -4346,8 +4401,11 @@
       <c r="BO18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -4549,8 +4607,11 @@
       <c r="BO19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -4752,8 +4813,11 @@
       <c r="BO20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -4955,8 +5019,11 @@
       <c r="BO21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -5158,8 +5225,11 @@
       <c r="BO22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -5361,8 +5431,11 @@
       <c r="BO23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -5564,8 +5637,11 @@
       <c r="BO24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -5767,8 +5843,11 @@
       <c r="BO25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -5970,8 +6049,11 @@
       <c r="BO26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -6173,8 +6255,11 @@
       <c r="BO27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -6376,8 +6461,11 @@
       <c r="BO28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -6579,8 +6667,11 @@
       <c r="BO29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -6782,8 +6873,11 @@
       <c r="BO30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -6985,8 +7079,11 @@
       <c r="BO31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -7188,8 +7285,11 @@
       <c r="BO32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -7391,8 +7491,11 @@
       <c r="BO33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP33" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -7594,20 +7697,23 @@
       <c r="BO34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="BP34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:68" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:68" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:68" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:68" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:68" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -7618,7 +7724,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E29950-B8AE-4925-B227-CCD0E2F526BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E6B2A9-60B8-4020-BEBB-1ECBEB1CB88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="55">
   <si>
     <t>Alunos</t>
   </si>
@@ -1314,6 +1314,9 @@
       <c r="BP3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BQ3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1520,6 +1523,9 @@
       <c r="BP4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BQ4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1726,6 +1732,9 @@
       <c r="BP5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BQ5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1932,6 +1941,9 @@
       <c r="BP6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BQ6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2138,6 +2150,9 @@
       <c r="BP7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BQ7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2344,6 +2359,9 @@
       <c r="BP8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BQ8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2550,6 +2568,9 @@
       <c r="BP9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BQ9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2756,6 +2777,9 @@
       <c r="BP10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BQ10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2962,6 +2986,9 @@
       <c r="BP11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BQ11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3168,6 +3195,9 @@
       <c r="BP12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BQ12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3374,6 +3404,9 @@
       <c r="BP13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BQ13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3580,6 +3613,9 @@
       <c r="BP14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BQ14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3786,6 +3822,9 @@
       <c r="BP15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BQ15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -3992,8 +4031,11 @@
       <c r="BP16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -4198,8 +4240,11 @@
       <c r="BP17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -4404,8 +4449,11 @@
       <c r="BP18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -4610,8 +4658,11 @@
       <c r="BP19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -4816,8 +4867,11 @@
       <c r="BP20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -5022,8 +5076,11 @@
       <c r="BP21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -5228,8 +5285,11 @@
       <c r="BP22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -5434,8 +5494,11 @@
       <c r="BP23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -5640,8 +5703,11 @@
       <c r="BP24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -5846,8 +5912,11 @@
       <c r="BP25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -6052,8 +6121,11 @@
       <c r="BP26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -6258,8 +6330,11 @@
       <c r="BP27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -6464,8 +6539,11 @@
       <c r="BP28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -6670,8 +6748,11 @@
       <c r="BP29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -6876,8 +6957,11 @@
       <c r="BP30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -7082,8 +7166,11 @@
       <c r="BP31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -7288,8 +7375,11 @@
       <c r="BP32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -7494,8 +7584,11 @@
       <c r="BP33" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -7700,20 +7793,23 @@
       <c r="BP34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:69" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:69" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:69" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:69" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:69" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -7724,7 +7820,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
+  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2025\ds\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E6B2A9-60B8-4020-BEBB-1ECBEB1CB88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77528328-189C-487F-AC98-98CD35E7BEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="55">
   <si>
     <t>Alunos</t>
   </si>
@@ -885,6 +885,12 @@
       <c r="BQ1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="BR1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1094,8 +1100,12 @@
       <c r="BQ2" s="2">
         <v>45952</v>
       </c>
-      <c r="BR2" s="2"/>
-      <c r="BS2" s="2"/>
+      <c r="BR2" s="2">
+        <v>45958</v>
+      </c>
+      <c r="BS2" s="2">
+        <v>45959</v>
+      </c>
       <c r="BT2" s="2"/>
       <c r="BU2" s="2"/>
       <c r="BV2" s="2"/>
@@ -1317,6 +1327,12 @@
       <c r="BQ3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BR3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1526,6 +1542,12 @@
       <c r="BQ4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BR4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1735,6 +1757,12 @@
       <c r="BQ5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BR5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1944,6 +1972,12 @@
       <c r="BQ6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BR6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2153,6 +2187,12 @@
       <c r="BQ7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BR7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2362,6 +2402,12 @@
       <c r="BQ8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BR8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2571,6 +2617,12 @@
       <c r="BQ9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BR9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2780,6 +2832,12 @@
       <c r="BQ10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BR10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -2989,6 +3047,12 @@
       <c r="BQ11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BR11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3198,6 +3262,12 @@
       <c r="BQ12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BR12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS12" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3407,6 +3477,12 @@
       <c r="BQ13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BR13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3616,6 +3692,12 @@
       <c r="BQ14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BR14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS14" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3825,6 +3907,12 @@
       <c r="BQ15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BR15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -4034,8 +4122,14 @@
       <c r="BQ16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -4243,8 +4337,14 @@
       <c r="BQ17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -4452,8 +4552,14 @@
       <c r="BQ18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -4661,8 +4767,14 @@
       <c r="BQ19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -4870,8 +4982,14 @@
       <c r="BQ20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -5079,8 +5197,14 @@
       <c r="BQ21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -5288,8 +5412,14 @@
       <c r="BQ22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -5497,8 +5627,14 @@
       <c r="BQ23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -5706,8 +5842,14 @@
       <c r="BQ24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -5915,8 +6057,14 @@
       <c r="BQ25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -6124,8 +6272,14 @@
       <c r="BQ26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -6333,8 +6487,14 @@
       <c r="BQ27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -6542,8 +6702,14 @@
       <c r="BQ28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -6751,8 +6917,14 @@
       <c r="BQ29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -6960,8 +7132,14 @@
       <c r="BQ30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -7169,8 +7347,14 @@
       <c r="BQ31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -7378,8 +7562,14 @@
       <c r="BQ32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -7587,8 +7777,14 @@
       <c r="BQ33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS33" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -7796,20 +7992,26 @@
       <c r="BQ34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="BR34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:71" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:71" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:71" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:71" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:71" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77528328-189C-487F-AC98-98CD35E7BEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147CCB45-09AC-4ECB-9FD8-01890AF8AFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3696,7 +3696,7 @@
         <v>3</v>
       </c>
       <c r="BS14" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147CCB45-09AC-4ECB-9FD8-01890AF8AFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697CF29B-839E-4746-915B-73A018A5368A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2479" uniqueCount="55">
   <si>
     <t>Alunos</t>
   </si>
@@ -678,7 +678,9 @@
     <col min="45" max="45" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="46" max="57" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="16384" width="6.7109375" style="1"/>
+    <col min="59" max="71" width="6.7109375" style="1"/>
+    <col min="72" max="73" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="74" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:83" x14ac:dyDescent="0.25">
@@ -891,6 +893,12 @@
       <c r="BS1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="BT1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1106,8 +1114,12 @@
       <c r="BS2" s="2">
         <v>45959</v>
       </c>
-      <c r="BT2" s="2"/>
-      <c r="BU2" s="2"/>
+      <c r="BT2" s="2">
+        <v>45965</v>
+      </c>
+      <c r="BU2" s="2">
+        <v>45966</v>
+      </c>
       <c r="BV2" s="2"/>
       <c r="BW2" s="2"/>
       <c r="BX2" s="2"/>
@@ -1333,6 +1345,12 @@
       <c r="BS3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BT3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1548,6 +1566,12 @@
       <c r="BS4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BT4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU4" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1763,6 +1787,12 @@
       <c r="BS5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BT5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1978,6 +2008,12 @@
       <c r="BS6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BT6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2193,6 +2229,12 @@
       <c r="BS7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BT7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2408,6 +2450,12 @@
       <c r="BS8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BT8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2623,6 +2671,12 @@
       <c r="BS9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BT9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2838,6 +2892,12 @@
       <c r="BS10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BT10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -3053,6 +3113,12 @@
       <c r="BS11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BT11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3268,6 +3334,12 @@
       <c r="BS12" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="BT12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3483,6 +3555,12 @@
       <c r="BS13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BT13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3698,6 +3776,12 @@
       <c r="BS14" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="BT14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -3913,6 +3997,12 @@
       <c r="BS15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BT15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -4128,8 +4218,14 @@
       <c r="BS16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -4343,8 +4439,14 @@
       <c r="BS17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -4558,8 +4660,14 @@
       <c r="BS18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -4773,8 +4881,14 @@
       <c r="BS19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -4988,8 +5102,14 @@
       <c r="BS20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -5203,8 +5323,14 @@
       <c r="BS21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -5418,8 +5544,14 @@
       <c r="BS22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -5633,8 +5765,14 @@
       <c r="BS23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -5848,8 +5986,14 @@
       <c r="BS24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -6063,8 +6207,14 @@
       <c r="BS25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -6278,8 +6428,14 @@
       <c r="BS26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -6493,8 +6649,14 @@
       <c r="BS27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -6708,8 +6870,14 @@
       <c r="BS28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -6923,8 +7091,14 @@
       <c r="BS29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -7138,8 +7312,14 @@
       <c r="BS30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -7353,8 +7533,14 @@
       <c r="BS31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -7568,8 +7754,14 @@
       <c r="BS32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -7783,8 +7975,14 @@
       <c r="BS33" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -7998,20 +8196,26 @@
       <c r="BS34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BT34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BU34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:73" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:73" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:73" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:73" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:73" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -8022,7 +8226,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697CF29B-839E-4746-915B-73A018A5368A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA96652C-C193-4CC2-B43E-C4741B0FF4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2479" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="55">
   <si>
     <t>Alunos</t>
   </si>
@@ -679,8 +679,8 @@
     <col min="46" max="57" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="59" max="71" width="6.7109375" style="1"/>
-    <col min="72" max="73" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="74" max="16384" width="6.7109375" style="1"/>
+    <col min="72" max="75" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="76" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:83" x14ac:dyDescent="0.25">
@@ -899,6 +899,12 @@
       <c r="BU1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="BV1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1120,8 +1126,12 @@
       <c r="BU2" s="2">
         <v>45966</v>
       </c>
-      <c r="BV2" s="2"/>
-      <c r="BW2" s="2"/>
+      <c r="BV2" s="2">
+        <v>45972</v>
+      </c>
+      <c r="BW2" s="2">
+        <v>45973</v>
+      </c>
       <c r="BX2" s="2"/>
       <c r="BY2" s="2"/>
       <c r="BZ2" s="2"/>
@@ -1351,6 +1361,9 @@
       <c r="BU3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BV3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1572,6 +1585,9 @@
       <c r="BU4" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="BV4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1793,6 +1809,9 @@
       <c r="BU5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BV5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -2014,6 +2033,9 @@
       <c r="BU6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BV6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2235,6 +2257,9 @@
       <c r="BU7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BV7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2456,6 +2481,9 @@
       <c r="BU8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BV8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2677,6 +2705,9 @@
       <c r="BU9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BV9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2898,6 +2929,9 @@
       <c r="BU10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BV10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -3119,6 +3153,9 @@
       <c r="BU11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BV11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3340,6 +3377,9 @@
       <c r="BU12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BV12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3561,6 +3601,9 @@
       <c r="BU13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BV13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3782,6 +3825,9 @@
       <c r="BU14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BV14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -4003,6 +4049,9 @@
       <c r="BU15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BV15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -4224,8 +4273,11 @@
       <c r="BU16" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -4445,8 +4497,11 @@
       <c r="BU17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -4666,8 +4721,11 @@
       <c r="BU18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -4887,8 +4945,11 @@
       <c r="BU19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -5108,8 +5169,11 @@
       <c r="BU20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -5329,8 +5393,11 @@
       <c r="BU21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -5550,8 +5617,11 @@
       <c r="BU22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -5771,8 +5841,11 @@
       <c r="BU23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -5992,8 +6065,11 @@
       <c r="BU24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -6213,8 +6289,11 @@
       <c r="BU25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -6434,8 +6513,11 @@
       <c r="BU26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -6655,8 +6737,11 @@
       <c r="BU27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -6876,8 +6961,11 @@
       <c r="BU28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -7097,8 +7185,11 @@
       <c r="BU29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -7318,8 +7409,11 @@
       <c r="BU30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -7539,8 +7633,11 @@
       <c r="BU31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -7760,8 +7857,11 @@
       <c r="BU32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -7981,8 +8081,11 @@
       <c r="BU33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -8202,20 +8305,23 @@
       <c r="BU34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BV34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:74" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:74" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:74" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:74" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:74" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA96652C-C193-4CC2-B43E-C4741B0FF4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05591B0-3471-4F36-B29C-DB79273F39EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2545" uniqueCount="55">
   <si>
     <t>Alunos</t>
   </si>
@@ -1364,6 +1364,9 @@
       <c r="BV3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BW3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1588,6 +1591,9 @@
       <c r="BV4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BW4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1812,6 +1818,9 @@
       <c r="BV5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BW5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -2036,6 +2045,9 @@
       <c r="BV6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BW6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2260,6 +2272,9 @@
       <c r="BV7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BW7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2484,6 +2499,9 @@
       <c r="BV8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BW8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2708,6 +2726,9 @@
       <c r="BV9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BW9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2932,6 +2953,9 @@
       <c r="BV10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BW10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -3156,6 +3180,9 @@
       <c r="BV11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BW11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3380,6 +3407,9 @@
       <c r="BV12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BW12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3604,6 +3634,9 @@
       <c r="BV13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BW13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3828,6 +3861,9 @@
       <c r="BV14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BW14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -4052,6 +4088,9 @@
       <c r="BV15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BW15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -4276,8 +4315,11 @@
       <c r="BV16" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -4500,8 +4542,11 @@
       <c r="BV17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -4724,8 +4769,11 @@
       <c r="BV18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -4948,8 +4996,11 @@
       <c r="BV19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -5172,8 +5223,11 @@
       <c r="BV20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -5396,8 +5450,11 @@
       <c r="BV21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -5620,8 +5677,11 @@
       <c r="BV22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -5844,8 +5904,11 @@
       <c r="BV23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -6068,8 +6131,11 @@
       <c r="BV24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -6292,8 +6358,11 @@
       <c r="BV25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -6516,8 +6585,11 @@
       <c r="BV26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -6740,8 +6812,11 @@
       <c r="BV27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -6964,8 +7039,11 @@
       <c r="BV28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -7188,8 +7266,11 @@
       <c r="BV29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -7412,8 +7493,11 @@
       <c r="BV30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -7636,8 +7720,11 @@
       <c r="BV31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -7860,8 +7947,11 @@
       <c r="BV32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -8084,8 +8174,11 @@
       <c r="BV33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -8308,20 +8401,23 @@
       <c r="BV34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BW34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:75" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:75" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:75" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:75" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:75" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -8332,7 +8428,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
+  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05591B0-3471-4F36-B29C-DB79273F39EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB9872D-1C02-42A9-A484-310E08633A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2545" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="55">
   <si>
     <t>Alunos</t>
   </si>
@@ -679,8 +679,8 @@
     <col min="46" max="57" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="59" max="71" width="6.7109375" style="1"/>
-    <col min="72" max="75" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="76" max="16384" width="6.7109375" style="1"/>
+    <col min="72" max="77" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="78" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:83" x14ac:dyDescent="0.25">
@@ -905,6 +905,12 @@
       <c r="BW1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="BX1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1132,8 +1138,12 @@
       <c r="BW2" s="2">
         <v>45973</v>
       </c>
-      <c r="BX2" s="2"/>
-      <c r="BY2" s="2"/>
+      <c r="BX2" s="2">
+        <v>45979</v>
+      </c>
+      <c r="BY2" s="2">
+        <v>45980</v>
+      </c>
       <c r="BZ2" s="2"/>
       <c r="CA2" s="2"/>
       <c r="CB2" s="2"/>
@@ -1367,6 +1377,9 @@
       <c r="BW3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BX3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1594,6 +1607,9 @@
       <c r="BW4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BX4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1821,6 +1837,9 @@
       <c r="BW5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BX5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -2048,6 +2067,9 @@
       <c r="BW6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BX6" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2275,6 +2297,9 @@
       <c r="BW7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BX7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2502,6 +2527,9 @@
       <c r="BW8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BX8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2729,6 +2757,9 @@
       <c r="BW9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BX9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2956,6 +2987,9 @@
       <c r="BW10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BX10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -3183,6 +3217,9 @@
       <c r="BW11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BX11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3410,6 +3447,9 @@
       <c r="BW12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BX12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3637,6 +3677,9 @@
       <c r="BW13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BX13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3864,6 +3907,9 @@
       <c r="BW14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BX14" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -4091,6 +4137,9 @@
       <c r="BW15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BX15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -4318,8 +4367,11 @@
       <c r="BW16" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -4545,8 +4597,11 @@
       <c r="BW17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -4772,8 +4827,11 @@
       <c r="BW18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -4999,8 +5057,11 @@
       <c r="BW19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -5226,8 +5287,11 @@
       <c r="BW20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -5453,8 +5517,11 @@
       <c r="BW21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -5680,8 +5747,11 @@
       <c r="BW22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -5907,8 +5977,11 @@
       <c r="BW23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -6134,8 +6207,11 @@
       <c r="BW24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -6361,8 +6437,11 @@
       <c r="BW25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -6588,8 +6667,11 @@
       <c r="BW26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -6815,8 +6897,11 @@
       <c r="BW27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -7042,8 +7127,11 @@
       <c r="BW28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -7269,8 +7357,11 @@
       <c r="BW29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -7496,8 +7587,11 @@
       <c r="BW30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX30" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -7723,8 +7817,11 @@
       <c r="BW31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -7950,8 +8047,11 @@
       <c r="BW32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -8177,8 +8277,11 @@
       <c r="BW33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -8404,20 +8507,23 @@
       <c r="BW34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BX34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:76" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:76" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:76" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:76" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:76" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -8428,7 +8534,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB9872D-1C02-42A9-A484-310E08633A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5A6F51-E2B0-4275-8BC1-05CC510EC5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3908,7 +3908,7 @@
         <v>3</v>
       </c>
       <c r="BX14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
@@ -7588,7 +7588,7 @@
         <v>3</v>
       </c>
       <c r="BX30" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:76" x14ac:dyDescent="0.25">
@@ -8534,7 +8534,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
+  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5A6F51-E2B0-4275-8BC1-05CC510EC5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1087E54-F276-4A60-A78A-C7A04F85B05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2644" uniqueCount="56">
   <si>
     <t>Alunos</t>
   </si>
@@ -203,6 +203,9 @@
   </si>
   <si>
     <t>2P</t>
+  </si>
+  <si>
+    <t>Qui</t>
   </si>
 </sst>
 </file>
@@ -679,8 +682,8 @@
     <col min="46" max="57" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="59" max="71" width="6.7109375" style="1"/>
-    <col min="72" max="77" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="78" max="16384" width="6.7109375" style="1"/>
+    <col min="72" max="78" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="79" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:83" x14ac:dyDescent="0.25">
@@ -911,6 +914,9 @@
       <c r="BY1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="BZ1" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="2" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1144,7 +1150,9 @@
       <c r="BY2" s="2">
         <v>45980</v>
       </c>
-      <c r="BZ2" s="2"/>
+      <c r="BZ2" s="2">
+        <v>45986</v>
+      </c>
       <c r="CA2" s="2"/>
       <c r="CB2" s="2"/>
       <c r="CC2" s="2"/>
@@ -1380,6 +1388,12 @@
       <c r="BX3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BY3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1610,6 +1624,12 @@
       <c r="BX4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BY4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1840,6 +1860,12 @@
       <c r="BX5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BY5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -2070,6 +2096,12 @@
       <c r="BX6" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="BY6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2300,6 +2332,12 @@
       <c r="BX7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BY7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2530,6 +2568,12 @@
       <c r="BX8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BY8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2760,6 +2804,12 @@
       <c r="BX9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BY9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2990,6 +3040,12 @@
       <c r="BX10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BY10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BZ10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -3220,6 +3276,12 @@
       <c r="BX11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BY11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3450,6 +3512,12 @@
       <c r="BX12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BY12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3680,6 +3748,12 @@
       <c r="BX13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BY13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3910,6 +3984,12 @@
       <c r="BX14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BY14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -4140,6 +4220,12 @@
       <c r="BX15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="BY15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -4370,8 +4456,14 @@
       <c r="BX16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -4600,8 +4692,14 @@
       <c r="BX17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -4830,8 +4928,14 @@
       <c r="BX18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -5060,8 +5164,14 @@
       <c r="BX19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -5290,8 +5400,14 @@
       <c r="BX20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -5520,8 +5636,14 @@
       <c r="BX21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -5750,8 +5872,14 @@
       <c r="BX22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -5980,8 +6108,14 @@
       <c r="BX23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -6210,8 +6344,14 @@
       <c r="BX24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -6440,8 +6580,14 @@
       <c r="BX25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -6670,8 +6816,14 @@
       <c r="BX26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -6900,8 +7052,14 @@
       <c r="BX27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -7130,8 +7288,14 @@
       <c r="BX28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -7360,8 +7524,14 @@
       <c r="BX29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -7590,8 +7760,14 @@
       <c r="BX30" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="31" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -7820,8 +7996,14 @@
       <c r="BX31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -8050,8 +8232,14 @@
       <c r="BX32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -8280,8 +8468,14 @@
       <c r="BX33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -8510,20 +8704,26 @@
       <c r="BX34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="BY34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BZ34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:78" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:78" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:78" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:78" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:78" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1087E54-F276-4A60-A78A-C7A04F85B05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0571CCFF-41DE-459E-BF34-3DBF01466447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4460,7 +4460,7 @@
         <v>3</v>
       </c>
       <c r="BZ16" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:78" x14ac:dyDescent="0.25">

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0571CCFF-41DE-459E-BF34-3DBF01466447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A583E4-DC1C-415F-B3FA-E620C3BFB1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A583E4-DC1C-415F-B3FA-E620C3BFB1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C300A00B-411C-4AD6-B39B-95B16F26A666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2644" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2677" uniqueCount="56">
   <si>
     <t>Alunos</t>
   </si>
@@ -682,8 +682,8 @@
     <col min="46" max="57" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="59" max="71" width="6.7109375" style="1"/>
-    <col min="72" max="78" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="79" max="16384" width="6.7109375" style="1"/>
+    <col min="72" max="79" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="80" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:83" x14ac:dyDescent="0.25">
@@ -915,6 +915,9 @@
         <v>36</v>
       </c>
       <c r="BZ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="CA1" s="1" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1153,7 +1156,9 @@
       <c r="BZ2" s="2">
         <v>45986</v>
       </c>
-      <c r="CA2" s="2"/>
+      <c r="CA2" s="2">
+        <v>45987</v>
+      </c>
       <c r="CB2" s="2"/>
       <c r="CC2" s="2"/>
       <c r="CD2" s="2"/>
@@ -1394,6 +1399,9 @@
       <c r="BZ3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CA3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1630,6 +1638,9 @@
       <c r="BZ4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CA4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1866,6 +1877,9 @@
       <c r="BZ5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CA5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -2102,6 +2116,9 @@
       <c r="BZ6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CA6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2338,6 +2355,9 @@
       <c r="BZ7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CA7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2574,6 +2594,9 @@
       <c r="BZ8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CA8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2810,6 +2833,9 @@
       <c r="BZ9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CA9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -3046,6 +3072,9 @@
       <c r="BZ10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CA10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -3282,6 +3311,9 @@
       <c r="BZ11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CA11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3518,6 +3550,9 @@
       <c r="BZ12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CA12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3754,6 +3789,9 @@
       <c r="BZ13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CA13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -3990,6 +4028,9 @@
       <c r="BZ14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CA14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -4226,6 +4267,9 @@
       <c r="BZ15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CA15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -4462,8 +4506,11 @@
       <c r="BZ16" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="17" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -4698,8 +4745,11 @@
       <c r="BZ17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -4934,8 +4984,11 @@
       <c r="BZ18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -5170,8 +5223,11 @@
       <c r="BZ19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -5406,8 +5462,11 @@
       <c r="BZ20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -5642,8 +5701,11 @@
       <c r="BZ21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -5878,8 +5940,11 @@
       <c r="BZ22" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -6114,8 +6179,11 @@
       <c r="BZ23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -6350,8 +6418,11 @@
       <c r="BZ24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -6586,8 +6657,11 @@
       <c r="BZ25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -6822,8 +6896,11 @@
       <c r="BZ26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -7058,8 +7135,11 @@
       <c r="BZ27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -7294,8 +7374,11 @@
       <c r="BZ28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -7530,8 +7613,11 @@
       <c r="BZ29" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -7766,8 +7852,11 @@
       <c r="BZ30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -8002,8 +8091,11 @@
       <c r="BZ31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -8238,8 +8330,11 @@
       <c r="BZ32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -8474,8 +8569,11 @@
       <c r="BZ33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -8710,20 +8808,23 @@
       <c r="BZ34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:79" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:79" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:79" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:79" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:79" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C300A00B-411C-4AD6-B39B-95B16F26A666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A467EE86-9215-4C33-AB37-4FD5AD1BF787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -664,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:CE39"/>
+  <dimension ref="A1:CC39"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -686,7 +686,7 @@
     <col min="80" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -921,7 +921,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
@@ -1161,10 +1161,8 @@
       </c>
       <c r="CB2" s="2"/>
       <c r="CC2" s="2"/>
-      <c r="CD2" s="2"/>
-      <c r="CE2" s="2"/>
-    </row>
-    <row r="3" spans="1:83" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>24126008</v>
       </c>
@@ -1403,7 +1401,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>24125990</v>
       </c>
@@ -1642,7 +1640,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>24125969</v>
       </c>
@@ -1881,7 +1879,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>24125996</v>
       </c>
@@ -2120,7 +2118,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>24125975</v>
       </c>
@@ -2359,7 +2357,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>24125978</v>
       </c>
@@ -2598,7 +2596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>24125993</v>
       </c>
@@ -2837,7 +2835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>24126043</v>
       </c>
@@ -3076,7 +3074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>24125985</v>
       </c>
@@ -3315,7 +3313,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>24125984</v>
       </c>
@@ -3554,7 +3552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>24125988</v>
       </c>
@@ -3793,7 +3791,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>24126459</v>
       </c>
@@ -4032,7 +4030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>24126094</v>
       </c>
@@ -4271,7 +4269,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>24126041</v>
       </c>
@@ -8835,7 +8833,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 AS1:XFD2 A3:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A467EE86-9215-4C33-AB37-4FD5AD1BF787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AA0DCF-E177-45CB-890E-6EF37E1E8408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2677" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2710" uniqueCount="56">
   <si>
     <t>Alunos</t>
   </si>
@@ -682,8 +682,8 @@
     <col min="46" max="57" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="59" max="71" width="6.7109375" style="1"/>
-    <col min="72" max="79" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="80" max="16384" width="6.7109375" style="1"/>
+    <col min="72" max="80" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="81" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:81" x14ac:dyDescent="0.25">
@@ -920,6 +920,9 @@
       <c r="CA1" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="CB1" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="2" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1159,7 +1162,9 @@
       <c r="CA2" s="2">
         <v>45987</v>
       </c>
-      <c r="CB2" s="2"/>
+      <c r="CB2" s="2">
+        <v>45993</v>
+      </c>
       <c r="CC2" s="2"/>
     </row>
     <row r="3" spans="1:81" x14ac:dyDescent="0.25">
@@ -1400,6 +1405,9 @@
       <c r="CA3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CB3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1639,6 +1647,9 @@
       <c r="CA4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CB4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1878,6 +1889,9 @@
       <c r="CA5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CB5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -2117,6 +2131,9 @@
       <c r="CA6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CB6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2356,6 +2373,9 @@
       <c r="CA7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CB7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2595,6 +2615,9 @@
       <c r="CA8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CB8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2834,6 +2857,9 @@
       <c r="CA9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CB9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -3073,6 +3099,9 @@
       <c r="CA10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CB10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -3312,6 +3341,9 @@
       <c r="CA11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CB11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3551,6 +3583,9 @@
       <c r="CA12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CB12" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="13" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3790,6 +3825,9 @@
       <c r="CA13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CB13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -4029,6 +4067,9 @@
       <c r="CA14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CB14" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -4268,6 +4309,9 @@
       <c r="CA15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CB15" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -4507,8 +4551,11 @@
       <c r="CA16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -4746,8 +4793,11 @@
       <c r="CA17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -4985,8 +5035,11 @@
       <c r="CA18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -5224,8 +5277,11 @@
       <c r="CA19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -5463,8 +5519,11 @@
       <c r="CA20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -5702,8 +5761,11 @@
       <c r="CA21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -5941,8 +6003,11 @@
       <c r="CA22" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -6180,8 +6245,11 @@
       <c r="CA23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -6419,8 +6487,11 @@
       <c r="CA24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -6658,8 +6729,11 @@
       <c r="CA25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -6897,8 +6971,11 @@
       <c r="CA26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -7136,8 +7213,11 @@
       <c r="CA27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -7375,8 +7455,11 @@
       <c r="CA28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -7614,8 +7697,11 @@
       <c r="CA29" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -7853,8 +7939,11 @@
       <c r="CA30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -8092,8 +8181,11 @@
       <c r="CA31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -8331,8 +8423,11 @@
       <c r="CA32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -8570,8 +8665,11 @@
       <c r="CA33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -8809,20 +8907,23 @@
       <c r="CA34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="CB34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:80" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:80" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:80" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:80" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -8833,7 +8934,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 AS1:XFD2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AA0DCF-E177-45CB-890E-6EF37E1E8408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F28EB2-357B-4B42-BA4F-D30697B17AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1406,7 +1406,7 @@
         <v>3</v>
       </c>
       <c r="CB3" s="1" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:81" x14ac:dyDescent="0.25">

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F28EB2-357B-4B42-BA4F-D30697B17AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D542EF-32A6-4EA7-BB28-A9FC5A16F05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2710" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2743" uniqueCount="56">
   <si>
     <t>Alunos</t>
   </si>
@@ -682,8 +682,8 @@
     <col min="46" max="57" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="59" max="71" width="6.7109375" style="1"/>
-    <col min="72" max="80" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="81" max="16384" width="6.7109375" style="1"/>
+    <col min="72" max="81" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="82" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:81" x14ac:dyDescent="0.25">
@@ -923,6 +923,9 @@
       <c r="CB1" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="CC1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1165,7 +1168,9 @@
       <c r="CB2" s="2">
         <v>45993</v>
       </c>
-      <c r="CC2" s="2"/>
+      <c r="CC2" s="2">
+        <v>45994</v>
+      </c>
     </row>
     <row r="3" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
@@ -1408,6 +1413,9 @@
       <c r="CB3" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="CC3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1650,6 +1658,9 @@
       <c r="CB4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CC4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1892,6 +1903,9 @@
       <c r="CB5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CC5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -2134,6 +2148,9 @@
       <c r="CB6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CC6" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2376,6 +2393,9 @@
       <c r="CB7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CC7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2618,6 +2638,9 @@
       <c r="CB8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CC8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2860,6 +2883,9 @@
       <c r="CB9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CC9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -3102,6 +3128,9 @@
       <c r="CB10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CC10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -3344,6 +3373,9 @@
       <c r="CB11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CC11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3586,6 +3618,9 @@
       <c r="CB12" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="CC12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3828,6 +3863,9 @@
       <c r="CB13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CC13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -4070,6 +4108,9 @@
       <c r="CB14" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="CC14" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="15" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -4312,6 +4353,9 @@
       <c r="CB15" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="CC15" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -4554,8 +4598,11 @@
       <c r="CB16" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -4796,8 +4843,11 @@
       <c r="CB17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -5038,8 +5088,11 @@
       <c r="CB18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -5280,8 +5333,11 @@
       <c r="CB19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -5522,8 +5578,11 @@
       <c r="CB20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -5764,8 +5823,11 @@
       <c r="CB21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -6006,8 +6068,11 @@
       <c r="CB22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -6248,8 +6313,11 @@
       <c r="CB23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC23" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -6490,8 +6558,11 @@
       <c r="CB24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -6732,8 +6803,11 @@
       <c r="CB25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -6974,8 +7048,11 @@
       <c r="CB26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -7216,8 +7293,11 @@
       <c r="CB27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -7456,10 +7536,13 @@
         <v>3</v>
       </c>
       <c r="CB28" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:80" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="CC28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -7698,10 +7781,13 @@
         <v>4</v>
       </c>
       <c r="CB29" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:80" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="CC29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -7942,8 +8028,11 @@
       <c r="CB30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC30" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -8184,8 +8273,11 @@
       <c r="CB31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -8426,8 +8518,11 @@
       <c r="CB32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -8668,8 +8763,11 @@
       <c r="CB33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -8910,20 +9008,23 @@
       <c r="CB34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="CC34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:81" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:81" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:81" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:81" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:81" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D542EF-32A6-4EA7-BB28-A9FC5A16F05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAF270A-6C5A-460F-B3F2-667FD65F4003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2743" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2777" uniqueCount="56">
   <si>
     <t>Alunos</t>
   </si>
@@ -127,9 +127,6 @@
     <t>Rhayssa Rhackelly Maria</t>
   </si>
   <si>
-    <t>Rodrigo Passberg de Oliveiro</t>
-  </si>
-  <si>
     <t>Steffany Giovanna da Silva Souza</t>
   </si>
   <si>
@@ -206,6 +203,9 @@
   </si>
   <si>
     <t>Qui</t>
+  </si>
+  <si>
+    <t>Rodrigo Passberg de Oliveira</t>
   </si>
 </sst>
 </file>
@@ -664,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:CC39"/>
+  <dimension ref="A1:CE39"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -682,254 +682,260 @@
     <col min="46" max="57" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="59" max="71" width="6.7109375" style="1"/>
-    <col min="72" max="81" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="82" max="16384" width="6.7109375" style="1"/>
+    <col min="72" max="83" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="84" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
       <c r="D1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="F1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="H1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="J1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="L1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="N1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="P1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="R1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="S1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="T1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="U1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="V1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="X1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="Z1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AA1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="AB1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AC1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="AD1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AE1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="AF1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AG1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="AH1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AI1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="AJ1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="AL1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AM1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="AN1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AO1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AO1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="AP1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AQ1" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="AR1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AS1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AS1" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="AT1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AU1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="AV1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AW1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AW1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="AX1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AY1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="AZ1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BA1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BA1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="BB1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BC1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BC1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="BD1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BE1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BE1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="BF1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BG1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BG1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="BH1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BI1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BI1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="BJ1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BK1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BK1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="BL1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BM1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BM1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="BN1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BO1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BO1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="BP1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BQ1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="BR1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BS1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BS1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="BT1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BU1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BU1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="BV1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BW1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BW1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="BX1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BY1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BY1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="BZ1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="CC1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="CA1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="CE1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="CC1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:81" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>1</v>
@@ -1171,8 +1177,14 @@
       <c r="CC2" s="2">
         <v>45994</v>
       </c>
-    </row>
-    <row r="3" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD2" s="2">
+        <v>46000</v>
+      </c>
+      <c r="CE2" s="2">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>24126008</v>
       </c>
@@ -1255,7 +1267,7 @@
         <v>3</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AC3" s="1" t="s">
         <v>3</v>
@@ -1324,7 +1336,7 @@
         <v>3</v>
       </c>
       <c r="AY3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AZ3" s="1" t="s">
         <v>3</v>
@@ -1411,13 +1423,16 @@
         <v>3</v>
       </c>
       <c r="CB3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="CC3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>24125990</v>
       </c>
@@ -1661,8 +1676,11 @@
       <c r="CC4" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>24125969</v>
       </c>
@@ -1906,8 +1924,11 @@
       <c r="CC5" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>24125996</v>
       </c>
@@ -1990,7 +2011,7 @@
         <v>3</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC6" s="1" t="s">
         <v>4</v>
@@ -2151,8 +2172,11 @@
       <c r="CC6" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD6" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>24125975</v>
       </c>
@@ -2396,8 +2420,11 @@
       <c r="CC7" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD7" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>24125978</v>
       </c>
@@ -2641,8 +2668,11 @@
       <c r="CC8" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD8" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>24125993</v>
       </c>
@@ -2722,7 +2752,7 @@
         <v>3</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AB9" s="1" t="s">
         <v>3</v>
@@ -2886,13 +2916,16 @@
       <c r="CC9" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD9" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>24126043</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1">
         <v>22</v>
@@ -3131,8 +3164,11 @@
       <c r="CC10" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD10" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>24125985</v>
       </c>
@@ -3376,8 +3412,11 @@
       <c r="CC11" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD11" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>24125984</v>
       </c>
@@ -3616,13 +3655,16 @@
         <v>3</v>
       </c>
       <c r="CB12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="CC12" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD12" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>24125988</v>
       </c>
@@ -3866,8 +3908,11 @@
       <c r="CC13" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD13" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>24126459</v>
       </c>
@@ -3890,7 +3935,7 @@
         <v>3</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>3</v>
@@ -3971,7 +4016,7 @@
         <v>3</v>
       </c>
       <c r="AI14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AJ14" s="1" t="s">
         <v>4</v>
@@ -3986,7 +4031,7 @@
         <v>3</v>
       </c>
       <c r="AN14" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AO14" s="1" t="s">
         <v>3</v>
@@ -4079,7 +4124,7 @@
         <v>3</v>
       </c>
       <c r="BS14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BT14" s="1" t="s">
         <v>3</v>
@@ -4109,10 +4154,13 @@
         <v>4</v>
       </c>
       <c r="CC14" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:81" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="CD14" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>24126094</v>
       </c>
@@ -4356,8 +4404,11 @@
       <c r="CC15" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD15" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>24126041</v>
       </c>
@@ -4416,7 +4467,7 @@
         <v>3</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="U16" s="1" t="s">
         <v>3</v>
@@ -4590,7 +4641,7 @@
         <v>3</v>
       </c>
       <c r="BZ16" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="CA16" s="1" t="s">
         <v>3</v>
@@ -4601,8 +4652,11 @@
       <c r="CC16" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -4712,7 +4766,7 @@
         <v>3</v>
       </c>
       <c r="AK17" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AL17" s="1" t="s">
         <v>3</v>
@@ -4846,13 +4900,16 @@
       <c r="CC17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" s="1">
         <v>17</v>
@@ -4948,7 +5005,7 @@
         <v>3</v>
       </c>
       <c r="AH18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AI18" s="1" t="s">
         <v>3</v>
@@ -5091,8 +5148,11 @@
       <c r="CC18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -5336,8 +5396,11 @@
       <c r="CC19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -5581,8 +5644,11 @@
       <c r="CC20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -5826,8 +5892,11 @@
       <c r="CC21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -5841,7 +5910,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>3</v>
@@ -6071,8 +6140,11 @@
       <c r="CC22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -6314,10 +6386,13 @@
         <v>3</v>
       </c>
       <c r="CC23" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:81" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="CD23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -6561,8 +6636,11 @@
       <c r="CC24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -6806,8 +6884,11 @@
       <c r="CC25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -6884,7 +6965,7 @@
         <v>3</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA26" s="1" t="s">
         <v>3</v>
@@ -7051,8 +7132,11 @@
       <c r="CC26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -7296,8 +7380,11 @@
       <c r="CC27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -7434,7 +7521,7 @@
         <v>3</v>
       </c>
       <c r="AT28" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AU28" s="1" t="s">
         <v>4</v>
@@ -7470,7 +7557,7 @@
         <v>3</v>
       </c>
       <c r="BF28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BG28" s="1" t="s">
         <v>3</v>
@@ -7541,13 +7628,16 @@
       <c r="CC28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C29" s="1">
         <v>13</v>
@@ -7721,13 +7811,13 @@
         <v>3</v>
       </c>
       <c r="BH29" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BI29" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BJ29" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BK29" s="1" t="s">
         <v>3</v>
@@ -7786,13 +7876,16 @@
       <c r="CC29" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" s="1">
         <v>32</v>
@@ -8014,7 +8107,7 @@
         <v>3</v>
       </c>
       <c r="BX30" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BY30" s="1" t="s">
         <v>3</v>
@@ -8029,15 +8122,18 @@
         <v>3</v>
       </c>
       <c r="CC30" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:81" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="CD30" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31" s="1">
         <v>14</v>
@@ -8276,13 +8372,16 @@
       <c r="CC31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="1">
         <v>15</v>
@@ -8521,13 +8620,16 @@
       <c r="CC32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" s="1">
         <v>16</v>
@@ -8766,13 +8868,16 @@
       <c r="CC33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD33" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="1">
         <v>33</v>
@@ -8826,7 +8931,7 @@
         <v>3</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="U34" s="1" t="s">
         <v>3</v>
@@ -9011,20 +9116,23 @@
       <c r="CC34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:81" x14ac:dyDescent="0.25">
+      <c r="CD34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:82" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:82" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:82" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:82" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:82" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -9035,7 +9143,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -9152,7 +9260,7 @@
         <v>24126043</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
@@ -9248,7 +9356,7 @@
         <v>24127560</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
@@ -9380,11 +9488,11 @@
         <v>24125981</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
-        <v>24125981,Rodrigo Passberg de Oliveiro</v>
+        <v>24125981,Rodrigo Passberg de Oliveira</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -9392,7 +9500,7 @@
         <v>24126030</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -9404,7 +9512,7 @@
         <v>24126277</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -9416,7 +9524,7 @@
         <v>24125982</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -9428,7 +9536,7 @@
         <v>24125986</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
@@ -9440,7 +9548,7 @@
         <v>24125994</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
@@ -9484,27 +9592,27 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>52</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -9513,7 +9621,7 @@
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -9522,10 +9630,10 @@
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -9534,10 +9642,10 @@
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -9545,13 +9653,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -9560,10 +9668,10 @@
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -9571,13 +9679,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -9586,22 +9694,22 @@
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -9610,10 +9718,10 @@
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -9623,7 +9731,7 @@
       <c r="B13" s="1"/>
       <c r="C13" s="7"/>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -9632,7 +9740,7 @@
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -9641,10 +9749,10 @@
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -9653,10 +9761,10 @@
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -9665,10 +9773,10 @@
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -9677,22 +9785,22 @@
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -9701,10 +9809,10 @@
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -9712,13 +9820,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -9727,10 +9835,10 @@
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -9745,13 +9853,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -9760,10 +9868,10 @@
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -9772,10 +9880,10 @@
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -9783,13 +9891,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -9797,13 +9905,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -9815,70 +9923,70 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="7"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAF270A-6C5A-460F-B3F2-667FD65F4003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D023A3-0A18-47A0-98CB-810D2FD510D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3661,7 +3661,7 @@
         <v>3</v>
       </c>
       <c r="CD12" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
@@ -4157,7 +4157,7 @@
         <v>38</v>
       </c>
       <c r="CD14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
@@ -6637,7 +6637,7 @@
         <v>3</v>
       </c>
       <c r="CD24" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:82" x14ac:dyDescent="0.25">
@@ -9143,7 +9143,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
+  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D023A3-0A18-47A0-98CB-810D2FD510D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D105C693-DDDE-472D-8A41-092998EEC184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2777" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2809" uniqueCount="56">
   <si>
     <t>Alunos</t>
   </si>
@@ -1431,6 +1431,9 @@
       <c r="CD3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CE3" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1679,6 +1682,9 @@
       <c r="CD4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CE4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1927,6 +1933,9 @@
       <c r="CD5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CE5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -2175,6 +2184,9 @@
       <c r="CD6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CE6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -2423,6 +2435,9 @@
       <c r="CD7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CE7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -2671,6 +2686,9 @@
       <c r="CD8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CE8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2919,6 +2937,9 @@
       <c r="CD9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CE9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -3167,6 +3188,9 @@
       <c r="CD10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CE10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -3415,6 +3439,9 @@
       <c r="CD11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CE11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -3663,6 +3690,9 @@
       <c r="CD12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CE12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -3911,6 +3941,9 @@
       <c r="CD13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CE13" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -4159,6 +4192,9 @@
       <c r="CD14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="CE14" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -4407,6 +4443,9 @@
       <c r="CD15" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="CE15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -4655,8 +4694,11 @@
       <c r="CD16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -4903,8 +4945,11 @@
       <c r="CD17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -5151,8 +5196,11 @@
       <c r="CD18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -5399,8 +5447,11 @@
       <c r="CD19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -5647,8 +5698,11 @@
       <c r="CD20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -5895,8 +5949,11 @@
       <c r="CD21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -6143,8 +6200,11 @@
       <c r="CD22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -6391,8 +6451,11 @@
       <c r="CD23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -6639,8 +6702,11 @@
       <c r="CD24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -6887,8 +6953,11 @@
       <c r="CD25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -7135,8 +7204,11 @@
       <c r="CD26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -7383,8 +7455,11 @@
       <c r="CD27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -7631,8 +7706,11 @@
       <c r="CD28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -7879,8 +7957,11 @@
       <c r="CD29" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -8127,8 +8208,11 @@
       <c r="CD30" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -8375,8 +8459,11 @@
       <c r="CD31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -8623,8 +8710,11 @@
       <c r="CD32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -8871,8 +8961,11 @@
       <c r="CD33" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE33" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:83" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -9119,20 +9212,23 @@
       <c r="CD34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="CE34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:83" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:83" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:83" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:83" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:83" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D105C693-DDDE-472D-8A41-092998EEC184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6414D3-1425-47C2-957F-B019E31A5C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6703,7 +6703,7 @@
         <v>3</v>
       </c>
       <c r="CE24" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:83" x14ac:dyDescent="0.25">

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6414D3-1425-47C2-957F-B019E31A5C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C39CD4-0F25-4B68-939E-B5941B48D813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8962,7 +8962,7 @@
         <v>4</v>
       </c>
       <c r="CE33" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:83" x14ac:dyDescent="0.25">

--- a/ds/chamada-3ano.xlsx
+++ b/ds/chamada-3ano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C39CD4-0F25-4B68-939E-B5941B48D813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6C1970-5CBB-484E-B7D5-B11A5AFD05EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2809" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="56">
   <si>
     <t>Alunos</t>
   </si>
@@ -664,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:CE39"/>
+  <dimension ref="A1:CF39"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -682,11 +682,11 @@
     <col min="46" max="57" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="59" max="71" width="6.7109375" style="1"/>
-    <col min="72" max="83" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="84" max="16384" width="6.7109375" style="1"/>
+    <col min="72" max="84" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="85" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -932,8 +932,11 @@
       <c r="CE1" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
@@ -1183,8 +1186,11 @@
       <c r="CE2" s="2">
         <v>46001</v>
       </c>
-    </row>
-    <row r="3" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF2" s="2">
+        <v>46007</v>
+      </c>
+    </row>
+    <row r="3" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>24126008</v>
       </c>
@@ -1434,8 +1440,11 @@
       <c r="CE3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>24125990</v>
       </c>
@@ -1685,8 +1694,11 @@
       <c r="CE4" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>24125969</v>
       </c>
@@ -1936,8 +1948,11 @@
       <c r="CE5" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>24125996</v>
       </c>
@@ -2187,8 +2202,11 @@
       <c r="CE6" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF6" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>24125975</v>
       </c>
@@ -2438,8 +2456,11 @@
       <c r="CE7" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF7" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>24125978</v>
       </c>
@@ -2689,8 +2710,11 @@
       <c r="CE8" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF8" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>24125993</v>
       </c>
@@ -2940,8 +2964,11 @@
       <c r="CE9" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF9" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>24126043</v>
       </c>
@@ -3191,8 +3218,11 @@
       <c r="CE10" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF10" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>24125985</v>
       </c>
@@ -3442,8 +3472,11 @@
       <c r="CE11" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF11" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>24125984</v>
       </c>
@@ -3693,8 +3726,11 @@
       <c r="CE12" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF12" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>24125988</v>
       </c>
@@ -3944,8 +3980,11 @@
       <c r="CE13" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF13" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>24126459</v>
       </c>
@@ -4195,8 +4234,11 @@
       <c r="CE14" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF14" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>24126094</v>
       </c>
@@ -4446,8 +4488,11 @@
       <c r="CE15" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF15" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>24126041</v>
       </c>
@@ -4697,8 +4742,11 @@
       <c r="CE16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126007</v>
       </c>
@@ -4948,8 +4996,11 @@
       <c r="CE17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24127560</v>
       </c>
@@ -5199,8 +5250,11 @@
       <c r="CE18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24126396</v>
       </c>
@@ -5450,8 +5504,11 @@
       <c r="CE19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24125987</v>
       </c>
@@ -5701,8 +5758,11 @@
       <c r="CE20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>24125974</v>
       </c>
@@ -5952,8 +6012,11 @@
       <c r="CE21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24125992</v>
       </c>
@@ -6203,8 +6266,11 @@
       <c r="CE22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125977</v>
       </c>
@@ -6454,8 +6520,11 @@
       <c r="CE23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125991</v>
       </c>
@@ -6705,8 +6774,11 @@
       <c r="CE24" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="25" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125989</v>
       </c>
@@ -6956,8 +7028,11 @@
       <c r="CE25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24125983</v>
       </c>
@@ -7207,8 +7282,11 @@
       <c r="CE26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125976</v>
       </c>
@@ -7458,8 +7536,11 @@
       <c r="CE27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24125967</v>
       </c>
@@ -7709,8 +7790,11 @@
       <c r="CE28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24125981</v>
       </c>
@@ -7960,8 +8044,11 @@
       <c r="CE29" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126030</v>
       </c>
@@ -8211,8 +8298,11 @@
       <c r="CE30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24126277</v>
       </c>
@@ -8462,8 +8552,11 @@
       <c r="CE31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125982</v>
       </c>
@@ -8713,8 +8806,11 @@
       <c r="CE32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125986</v>
       </c>
@@ -8964,8 +9060,11 @@
       <c r="CE33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125994</v>
       </c>
@@ -9215,20 +9314,23 @@
       <c r="CE34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:83" x14ac:dyDescent="0.25">
+      <c r="CF34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:84" x14ac:dyDescent="0.25">
       <c r="AR35" s="6"/>
     </row>
-    <row r="36" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:84" x14ac:dyDescent="0.25">
       <c r="AR36" s="6"/>
     </row>
-    <row r="37" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:84" x14ac:dyDescent="0.25">
       <c r="AR37" s="6"/>
     </row>
-    <row r="38" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:84" x14ac:dyDescent="0.25">
       <c r="AR38" s="6"/>
     </row>
-    <row r="39" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:84" x14ac:dyDescent="0.25">
       <c r="AR39" s="6"/>
     </row>
   </sheetData>
@@ -9239,7 +9341,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A1 D1:AR1 AS1:XFD2 A2:AR2 A3:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:AR1 A2:AR2 A3:XFD1048576 AS1:XFD2">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
